--- a/proposal/collaboration/collaboration_min.xlsx
+++ b/proposal/collaboration/collaboration_min.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/misunmin/proj/qq/collaboration/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/misunmin/proj/genesis21b/proposal/collaboration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9B69A0-B53E-0C4C-891E-3B949F1A18E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F34D52B0-3720-924C-968B-ACC33436C0AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7220" yWindow="660" windowWidth="30240" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4200" yWindow="660" windowWidth="30240" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="3" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="151">
   <si>
     <r>
       <rPr>
@@ -215,424 +215,325 @@
     <t>advisee</t>
   </si>
   <si>
-    <t>Alber</t>
-  </si>
-  <si>
     <t>David</t>
   </si>
   <si>
-    <t>Cohort 4</t>
-  </si>
-  <si>
-    <t>Advisee</t>
-  </si>
-  <si>
-    <t>Bell</t>
-  </si>
-  <si>
-    <t>Nathan</t>
-  </si>
-  <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>Chaudhry</t>
-  </si>
-  <si>
-    <t>Jehanzeb</t>
-  </si>
-  <si>
-    <t>University of New Mexico</t>
-  </si>
-  <si>
-    <t>Lai</t>
-  </si>
-  <si>
-    <t>James</t>
-  </si>
-  <si>
-    <t>Microsoft</t>
-  </si>
-  <si>
-    <t>Kimura</t>
-  </si>
-  <si>
-    <t>Yuki</t>
-  </si>
-  <si>
-    <t>OSIsoft</t>
-  </si>
-  <si>
-    <t>Dalton</t>
-  </si>
-  <si>
-    <t>Steven</t>
-  </si>
-  <si>
-    <t>Nvidia</t>
-  </si>
-  <si>
-    <t>Schroder</t>
-  </si>
-  <si>
-    <t>Jacob</t>
-  </si>
-  <si>
-    <t>Reisner</t>
-  </si>
-  <si>
     <t>Andrew</t>
   </si>
   <si>
     <t>Lawrence Livermore National Laboratory</t>
   </si>
   <si>
-    <t>Sentz</t>
-  </si>
-  <si>
-    <t>Peter</t>
-  </si>
-  <si>
-    <t>Brown University</t>
-  </si>
-  <si>
-    <t>Beams</t>
-  </si>
-  <si>
-    <t>Natalie</t>
-  </si>
-  <si>
-    <t>University of Tennessee - Knoxville</t>
-  </si>
-  <si>
-    <t>Bienz</t>
-  </si>
-  <si>
-    <t>Amanda</t>
-  </si>
-  <si>
-    <t>Calhoun</t>
-  </si>
-  <si>
-    <t>Jon</t>
-  </si>
-  <si>
-    <t>Clemson University</t>
-  </si>
-  <si>
-    <t>Samfass</t>
-  </si>
-  <si>
-    <t>Philipp</t>
-  </si>
-  <si>
-    <t>TU Münich</t>
-  </si>
-  <si>
-    <t>Hug</t>
-  </si>
-  <si>
-    <t>Adam</t>
-  </si>
-  <si>
-    <t>Matlab</t>
-  </si>
-  <si>
-    <t>Wrobel</t>
-  </si>
-  <si>
-    <t>Matt</t>
-  </si>
-  <si>
-    <t>Amazon</t>
-  </si>
-  <si>
-    <t>Gibson</t>
-  </si>
-  <si>
-    <t>Thomas</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>Ibeid</t>
-  </si>
-  <si>
-    <t>Huda</t>
-  </si>
-  <si>
-    <t>Intel</t>
-  </si>
-  <si>
-    <t>Manteuffel</t>
-  </si>
-  <si>
-    <t>Tom</t>
-  </si>
-  <si>
-    <t>McCormick</t>
-  </si>
-  <si>
-    <t>Steve</t>
-  </si>
-  <si>
-    <t>University of Colorado at Boulder</t>
-  </si>
-  <si>
-    <t>Advisor</t>
-  </si>
-  <si>
-    <t>Shadid</t>
-  </si>
-  <si>
     <t>John</t>
   </si>
   <si>
-    <t>Falgout</t>
-  </si>
-  <si>
-    <t>Rob</t>
-  </si>
-  <si>
-    <t>Los Alamos National Laboratory</t>
-  </si>
-  <si>
-    <t>Sandia National Laboratory</t>
-  </si>
-  <si>
-    <t>Zaman</t>
-  </si>
-  <si>
-    <t>Tareq</t>
-  </si>
-  <si>
-    <t>Memorial Univeristy of Newfoundland</t>
-  </si>
-  <si>
-    <t>MacLachlan</t>
-  </si>
-  <si>
-    <t>Scott</t>
-  </si>
-  <si>
-    <t>De Sterck</t>
-  </si>
-  <si>
-    <t>Hans</t>
-  </si>
-  <si>
-    <t>University of Waterloo</t>
-  </si>
-  <si>
-    <t>Adler</t>
-  </si>
-  <si>
-    <t>Tufts University</t>
-  </si>
-  <si>
-    <t>Moulton</t>
-  </si>
-  <si>
-    <t>MacArt</t>
-  </si>
-  <si>
-    <t>Notre Dame</t>
-  </si>
-  <si>
-    <t>Janna</t>
-  </si>
-  <si>
-    <t>Carlo</t>
-  </si>
-  <si>
-    <t>University of Padova</t>
-  </si>
-  <si>
-    <t>Franceschini</t>
-  </si>
-  <si>
-    <t>Andrea</t>
-  </si>
-  <si>
-    <t>He</t>
-  </si>
-  <si>
-    <t>Yunhui</t>
-  </si>
-  <si>
-    <t>Gardner</t>
-  </si>
-  <si>
-    <t>Woodward</t>
-  </si>
-  <si>
-    <t>Carol</t>
-  </si>
-  <si>
-    <t>Day</t>
-  </si>
-  <si>
-    <t>Marc</t>
-  </si>
-  <si>
-    <t>Beckwith</t>
-  </si>
-  <si>
     <t>Kris</t>
   </si>
   <si>
     <t>Patel</t>
   </si>
   <si>
-    <t>Ravi</t>
-  </si>
-  <si>
-    <t>Southworth</t>
-  </si>
-  <si>
-    <t>Ben</t>
-  </si>
-  <si>
-    <t>Berndt</t>
-  </si>
-  <si>
-    <t>Markus</t>
-  </si>
-  <si>
-    <t>Horn</t>
-  </si>
-  <si>
-    <t>Fulp</t>
-  </si>
-  <si>
-    <t>Einar</t>
-  </si>
-  <si>
-    <t>Dakota</t>
-  </si>
-  <si>
-    <t>unknown</t>
-  </si>
-  <si>
-    <t>Glimberg</t>
-  </si>
-  <si>
     <t>Stefan</t>
   </si>
   <si>
-    <t>DTU</t>
-  </si>
-  <si>
-    <t>Engsig-Karup</t>
-  </si>
-  <si>
-    <t>Alan</t>
-  </si>
-  <si>
-    <t>Cappello</t>
-  </si>
-  <si>
-    <t>Franck</t>
-  </si>
-  <si>
     <t>Argonne National Laboratory</t>
   </si>
   <si>
-    <t>Cyr</t>
-  </si>
-  <si>
-    <t>Eric</t>
-  </si>
-  <si>
-    <t>Siefert</t>
-  </si>
-  <si>
-    <t>Chris</t>
-  </si>
-  <si>
-    <t>Olson</t>
-  </si>
-  <si>
-    <t>Luke</t>
-  </si>
-  <si>
-    <t>0000-0002-5283-6104</t>
-  </si>
-  <si>
     <t>University of Illinois Urbana-Champaign</t>
   </si>
   <si>
-    <t>Tuminaro</t>
-  </si>
-  <si>
-    <t>Ray</t>
-  </si>
-  <si>
-    <t>Graham</t>
-  </si>
-  <si>
-    <t>Harper</t>
-  </si>
-  <si>
-    <t>Stephen</t>
-  </si>
-  <si>
-    <t>Lockhart</t>
-  </si>
-  <si>
-    <t>Shelby</t>
-  </si>
-  <si>
     <t>Voronin</t>
   </si>
   <si>
-    <t>Alexey</t>
-  </si>
-  <si>
-    <t>Karniadakis</t>
-  </si>
-  <si>
-    <t>George</t>
-  </si>
-  <si>
-    <t>Allen</t>
-  </si>
-  <si>
-    <t>Jefferety</t>
-  </si>
-  <si>
-    <t>National Laboratory of the Rockies</t>
-  </si>
-  <si>
     <t>Jed</t>
   </si>
   <si>
-    <t>Diener</t>
-  </si>
-  <si>
-    <t>Matthias</t>
-  </si>
-  <si>
-    <t>Smith</t>
-  </si>
-  <si>
-    <t>University of Illinois</t>
-  </si>
-  <si>
-    <t>Campbell</t>
-  </si>
-  <si>
-    <t>Min, Min</t>
-  </si>
-  <si>
-    <t>Olson, Luke</t>
-  </si>
-  <si>
-    <t>lukeo@illinois.edu</t>
-  </si>
-  <si>
     <t>Min, Misun</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Misun</t>
+  </si>
+  <si>
+    <t>Fischer</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>Kerkemeier</t>
+  </si>
+  <si>
+    <t>Tomboulides</t>
+  </si>
+  <si>
+    <t>Ananias</t>
+  </si>
+  <si>
+    <t>Aristotle University of Thessaloniki</t>
+  </si>
+  <si>
+    <t>Kolev</t>
+  </si>
+  <si>
+    <t>Tzanio</t>
+  </si>
+  <si>
+    <t>Dobrev</t>
+  </si>
+  <si>
+    <t>Veselin</t>
+  </si>
+  <si>
+    <t>Camier</t>
+  </si>
+  <si>
+    <t>Jean-Sylvain</t>
+  </si>
+  <si>
+    <t>Sprague</t>
+  </si>
+  <si>
+    <t>National Renewable Energy Laboratory</t>
+  </si>
+  <si>
+    <t>Brazell</t>
+  </si>
+  <si>
+    <t>Churchfield</t>
+  </si>
+  <si>
+    <t>Lehmkuhl</t>
+  </si>
+  <si>
+    <t>Oriol</t>
+  </si>
+  <si>
+    <t>Barcelona Supercomputing Center</t>
+  </si>
+  <si>
+    <t>Warburton</t>
+  </si>
+  <si>
+    <t>Tim</t>
+  </si>
+  <si>
+    <t>Virginia Tech</t>
+  </si>
+  <si>
+    <t>Chalmers</t>
+  </si>
+  <si>
+    <t>Noel</t>
+  </si>
+  <si>
+    <t>AMD Research</t>
+  </si>
+  <si>
+    <t>Yuan</t>
+  </si>
+  <si>
+    <t>Haomin</t>
+  </si>
+  <si>
+    <t>Shaver</t>
+  </si>
+  <si>
+    <t>Dillon</t>
+  </si>
+  <si>
+    <t>Obabko</t>
+  </si>
+  <si>
+    <t>Aleksandr</t>
+  </si>
+  <si>
+    <t>Rowe</t>
+  </si>
+  <si>
+    <t>Balakrishnan</t>
+  </si>
+  <si>
+    <t>Ramesh</t>
+  </si>
+  <si>
+    <t>Siegel</t>
+  </si>
+  <si>
+    <t>Jun</t>
+  </si>
+  <si>
+    <t>Feng</t>
+  </si>
+  <si>
+    <t>Kotamarthi</t>
+  </si>
+  <si>
+    <t>Rao</t>
+  </si>
+  <si>
+    <t>Novak</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>Saumil</t>
+  </si>
+  <si>
+    <t>Gaston</t>
+  </si>
+  <si>
+    <t>Derek</t>
+  </si>
+  <si>
+    <t>Idaho National Laboratory</t>
+  </si>
+  <si>
+    <t>Karakus</t>
+  </si>
+  <si>
+    <t>Ali</t>
+  </si>
+  <si>
+    <t>Middle East Technical University</t>
+  </si>
+  <si>
+    <t>Dutta</t>
+  </si>
+  <si>
+    <t>Som</t>
+  </si>
+  <si>
+    <t>Utah State University</t>
+  </si>
+  <si>
+    <t>Tsuji</t>
+  </si>
+  <si>
+    <t>Miwako</t>
+  </si>
+  <si>
+    <t>RIKEN, Japan</t>
+  </si>
+  <si>
+    <t>Sato</t>
+  </si>
+  <si>
+    <t>Mitsuhisa</t>
+  </si>
+  <si>
+    <t>Swirydowicz</t>
+  </si>
+  <si>
+    <t>Kasia</t>
+  </si>
+  <si>
+    <t>Pacific Northwest National Laboratory</t>
+  </si>
+  <si>
+    <t>University of Colorado Boulder</t>
+  </si>
+  <si>
+    <t>Kronbichler</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>University of Ausburg</t>
+  </si>
+  <si>
+    <t>Holmen</t>
+  </si>
+  <si>
+    <t>Oak Ridge National Laboratory</t>
+  </si>
+  <si>
+    <t>Chang</t>
+  </si>
+  <si>
+    <t>Kyoungsik</t>
+  </si>
+  <si>
+    <t>University of Ulsan, Korea</t>
+  </si>
+  <si>
+    <t>Chun</t>
+  </si>
+  <si>
+    <t>Sehun</t>
+  </si>
+  <si>
+    <t>Yonsei University, Korea</t>
+  </si>
+  <si>
+    <t>Lee</t>
+  </si>
+  <si>
+    <t>Taehun</t>
+  </si>
+  <si>
+    <t>The City College of New York - CUNY</t>
+  </si>
+  <si>
+    <t>Nicholls</t>
+  </si>
+  <si>
+    <t>University of Illinois at Chicago</t>
+  </si>
+  <si>
+    <t>Levesque</t>
+  </si>
+  <si>
+    <t>Supercomputing Center of Excellence at Cray Inc</t>
+  </si>
+  <si>
+    <t>Santosa</t>
+  </si>
+  <si>
+    <t>Fadil</t>
+  </si>
+  <si>
+    <t>Johns Hopkins University</t>
+  </si>
+  <si>
+    <t>Guo</t>
+  </si>
+  <si>
+    <t>Dahai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intel </t>
+  </si>
+  <si>
+    <t>Kirill</t>
+  </si>
+  <si>
+    <t>Pazner</t>
+  </si>
+  <si>
+    <t>Will</t>
+  </si>
+  <si>
+    <t>Portland State University</t>
+  </si>
+  <si>
+    <t>Posey</t>
+  </si>
+  <si>
+    <t>Stan</t>
+  </si>
+  <si>
+    <t>NVIDIA</t>
+  </si>
+  <si>
+    <t>mmin@mcs.anl.gov</t>
+  </si>
+  <si>
+    <t>0000-0002-5646-5689</t>
   </si>
 </sst>
 </file>
@@ -1258,9 +1159,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1270,8 +1168,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1279,27 +1186,19 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="9">
     <dxf>
       <fill>
         <patternFill>
@@ -1328,6 +1227,26 @@
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1666,51 +1585,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="46"/>
+      <c r="B1" s="45"/>
       <c r="C1" s="47" t="s">
-        <v>151</v>
+        <v>51</v>
       </c>
       <c r="D1" s="47"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="45"/>
       <c r="C2" s="47" t="s">
-        <v>183</v>
+        <v>55</v>
       </c>
       <c r="D2" s="47"/>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="46"/>
+      <c r="B3" s="45"/>
       <c r="C3" s="47" t="s">
-        <v>181</v>
+        <v>55</v>
       </c>
       <c r="D3" s="47"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="54" t="s">
-        <v>182</v>
+      <c r="B4" s="45"/>
+      <c r="C4" s="46" t="s">
+        <v>149</v>
       </c>
       <c r="D4" s="47"/>
     </row>
     <row r="5" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="45"/>
+      <c r="B6" s="44"/>
       <c r="C6" s="39"/>
       <c r="D6" s="40"/>
     </row>
@@ -1730,16 +1649,16 @@
     </row>
     <row r="8" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="29" t="s">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>157</v>
+        <v>57</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>159</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -1869,7 +1788,7 @@
     <mergeCell ref="C3:D3"/>
   </mergeCells>
   <conditionalFormatting sqref="A8:D27">
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="8" priority="2">
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1898,254 +1817,279 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="46"/>
+      <c r="B1" s="45"/>
       <c r="C1" s="47" t="s">
-        <v>151</v>
+        <v>51</v>
       </c>
       <c r="D1" s="47"/>
       <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="45"/>
       <c r="C2" s="47" t="s">
-        <v>180</v>
+        <v>55</v>
       </c>
       <c r="D2" s="47"/>
       <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="46"/>
+      <c r="B3" s="45"/>
       <c r="C3" s="47" t="s">
-        <v>181</v>
+        <v>55</v>
       </c>
       <c r="D3" s="47"/>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="46" t="s">
+    <row r="4" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="54" t="s">
-        <v>182</v>
+      <c r="B4" s="45"/>
+      <c r="C4" s="46" t="s">
+        <v>149</v>
       </c>
       <c r="D4" s="47"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="48" t="s">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="50" t="str">
-        <f>"Collaborator Table - "&amp;C1&amp;" ("&amp;C2&amp;")"</f>
-        <v>Collaborator Table - Argonne National Laboratory (Min, Min)</v>
-      </c>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="51"/>
-    </row>
-    <row r="7" spans="1:8" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
+      <c r="B5" s="51"/>
+      <c r="C5" s="48" t="e">
+        <f>"Collaborator Table - "&amp;#REF!&amp;" ("&amp;C1&amp;")"</f>
+        <v>#REF!</v>
+      </c>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="49"/>
+    </row>
+    <row r="6" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B6" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C6" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D6" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E6" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="F6" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="G6" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="24" t="s">
+      <c r="H6" s="24" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="36.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="19">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="G8" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="H8" s="19">
-        <v>2010</v>
+        <v>56</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="s">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C9" s="42" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>49</v>
-      </c>
-      <c r="E9" s="41"/>
-      <c r="F9" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="7">
-        <v>2020</v>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="19">
+        <v>2023</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="14" t="s">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C10" s="42" t="s">
-        <v>51</v>
-      </c>
-      <c r="D10" s="41" t="s">
-        <v>52</v>
-      </c>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="7">
+        <v>57</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="19">
         <v>2023</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C11" s="42" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="H11" s="7">
-        <v>2012</v>
+      <c r="B11" s="54" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="17"/>
+      <c r="F11" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="19">
+        <v>2023</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="14" t="s">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C12" s="42" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="41" t="s">
-        <v>58</v>
-      </c>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="H12" s="7">
-        <v>2013</v>
+      <c r="C12" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G12" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="19">
+        <v>2023</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" s="41" t="s">
-        <v>61</v>
-      </c>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="7">
+        <v>57</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="19">
         <v>2023</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D14" s="41" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="E14" s="41"/>
       <c r="F14" s="41" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="H14" s="7">
         <v>2023</v>
@@ -2153,47 +2097,47 @@
     </row>
     <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="41" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="D15" s="42" t="s">
+        <v>32</v>
       </c>
       <c r="E15" s="41"/>
       <c r="F15" s="41" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="H15" s="7">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" s="41" t="s">
-        <v>69</v>
+        <v>73</v>
+      </c>
+      <c r="D16" s="42" t="s">
+        <v>73</v>
       </c>
       <c r="E16" s="41"/>
       <c r="F16" s="41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="H16" s="7">
         <v>2023</v>
@@ -2201,47 +2145,47 @@
     </row>
     <row r="17" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C17" s="42" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D17" s="41" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E17" s="41"/>
       <c r="F17" s="41" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="H17" s="7">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C18" s="42" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D18" s="41" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E18" s="41"/>
       <c r="F18" s="41" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="H18" s="7">
         <v>2023</v>
@@ -2249,215 +2193,215 @@
     </row>
     <row r="19" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C19" s="42" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D19" s="41" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E19" s="41"/>
       <c r="F19" s="41" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="H19" s="7">
-        <v>2019</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D20" s="41" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E20" s="41"/>
       <c r="F20" s="41" t="s">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="H20" s="7">
-        <v>2016</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D21" s="41" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E21" s="41"/>
       <c r="F21" s="41" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="H21" s="7">
-        <v>2014</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D22" s="41" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E22" s="41"/>
       <c r="F22" s="41" t="s">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="H22" s="7">
-        <v>2012</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C23" s="42" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D23" s="41" t="s">
-        <v>89</v>
+        <v>48</v>
       </c>
       <c r="E23" s="41"/>
       <c r="F23" s="41" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="H23" s="7">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C24" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" s="41" t="s">
         <v>91</v>
-      </c>
-      <c r="D24" s="41" t="s">
-        <v>92</v>
       </c>
       <c r="E24" s="41"/>
       <c r="F24" s="41" t="s">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="H24" s="7">
-        <v>2019</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C25" s="42" t="s">
-        <v>165</v>
+        <v>92</v>
       </c>
       <c r="D25" s="41" t="s">
-        <v>166</v>
+        <v>45</v>
       </c>
       <c r="E25" s="41"/>
       <c r="F25" s="41" t="s">
-        <v>90</v>
+        <v>51</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="H25" s="7">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C26" s="42" t="s">
-        <v>167</v>
+        <v>93</v>
       </c>
       <c r="D26" s="41" t="s">
-        <v>168</v>
+        <v>94</v>
       </c>
       <c r="E26" s="41"/>
       <c r="F26" s="41" t="s">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="H26" s="7">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D27" s="41" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E27" s="41"/>
       <c r="F27" s="41" t="s">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="H27" s="7">
         <v>2023</v>
@@ -2465,23 +2409,23 @@
     </row>
     <row r="28" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D28" s="41" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E28" s="41"/>
-      <c r="F28" s="43" t="s">
-        <v>98</v>
+      <c r="F28" s="41" t="s">
+        <v>51</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="H28" s="7">
         <v>2023</v>
@@ -2489,20 +2433,20 @@
     </row>
     <row r="29" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="D29" s="41" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E29" s="41"/>
       <c r="F29" s="41" t="s">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>20</v>
@@ -2513,23 +2457,23 @@
     </row>
     <row r="30" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B30" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D30" s="41" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E30" s="41"/>
       <c r="F30" s="41" t="s">
-        <v>67</v>
+        <v>102</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="H30" s="7">
         <v>2023</v>
@@ -2537,143 +2481,143 @@
     </row>
     <row r="31" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B31" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>160</v>
+        <v>103</v>
       </c>
       <c r="D31" s="41" t="s">
-        <v>161</v>
+        <v>104</v>
       </c>
       <c r="E31" s="41"/>
       <c r="F31" s="41" t="s">
         <v>105</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="H31" s="7">
-        <v>2024</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C32" s="42" t="s">
-        <v>163</v>
+        <v>106</v>
       </c>
       <c r="D32" s="41" t="s">
-        <v>162</v>
+        <v>107</v>
       </c>
       <c r="E32" s="41"/>
       <c r="F32" s="41" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="H32" s="7">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C33" s="42" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="D33" s="41" t="s">
-        <v>164</v>
+        <v>110</v>
       </c>
       <c r="E33" s="41"/>
       <c r="F33" s="41" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="H33" s="7">
-        <v>2024</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C34" s="42" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="D34" s="41" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E34" s="41"/>
       <c r="F34" s="41" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>37</v>
       </c>
       <c r="H34" s="7">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C35" s="42" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D35" s="41" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E35" s="41"/>
       <c r="F35" s="41" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="G35" s="6" t="s">
         <v>37</v>
       </c>
       <c r="H35" s="7">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C36" s="42" t="s">
-        <v>111</v>
+        <v>38</v>
       </c>
       <c r="D36" s="41" t="s">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="E36" s="41"/>
       <c r="F36" s="41" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H36" s="7">
         <v>2023</v>
@@ -2681,71 +2625,71 @@
     </row>
     <row r="37" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B37" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C37" s="42" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D37" s="41" t="s">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="E37" s="41"/>
       <c r="F37" s="41" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>37</v>
       </c>
       <c r="H37" s="7">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C38" s="42" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D38" s="41" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E38" s="41"/>
       <c r="F38" s="41" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H38" s="7">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C39" s="42" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D39" s="41" t="s">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="E39" s="41"/>
       <c r="F39" s="41" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H39" s="7">
         <v>2023</v>
@@ -2753,23 +2697,23 @@
     </row>
     <row r="40" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C40" s="42" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D40" s="41" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E40" s="41"/>
       <c r="F40" s="41" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H40" s="7">
         <v>2023</v>
@@ -2777,23 +2721,23 @@
     </row>
     <row r="41" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B41" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C41" s="42" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D41" s="41" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E41" s="41"/>
       <c r="F41" s="41" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="G41" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H41" s="7">
         <v>2023</v>
@@ -2801,95 +2745,95 @@
     </row>
     <row r="42" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C42" s="42" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D42" s="41" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="E42" s="41"/>
       <c r="F42" s="41" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H42" s="7">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B43" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C43" s="42" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D43" s="41" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E43" s="41"/>
       <c r="F43" s="41" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H43" s="7">
-        <v>2023</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B44" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C44" s="42" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="D44" s="41" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E44" s="41"/>
       <c r="F44" s="41" t="s">
-        <v>67</v>
+        <v>138</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H44" s="7">
-        <v>2023</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B45" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C45" s="42" t="s">
-        <v>89</v>
+        <v>139</v>
       </c>
       <c r="D45" s="41" t="s">
-        <v>61</v>
+        <v>140</v>
       </c>
       <c r="E45" s="41"/>
       <c r="F45" s="41" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H45" s="7">
         <v>2023</v>
@@ -2897,23 +2841,23 @@
     </row>
     <row r="46" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C46" s="42" t="s">
-        <v>129</v>
+        <v>53</v>
       </c>
       <c r="D46" s="41" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="E46" s="41"/>
       <c r="F46" s="41" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H46" s="7">
         <v>2023</v>
@@ -2921,23 +2865,23 @@
     </row>
     <row r="47" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B47" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C47" s="42" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="D47" s="41" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="E47" s="41"/>
       <c r="F47" s="41" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="G47" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H47" s="7">
         <v>2023</v>
@@ -2945,1005 +2889,742 @@
     </row>
     <row r="48" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B48" s="15" t="s">
-        <v>157</v>
+        <v>56</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="C48" s="42" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="D48" s="41" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="E48" s="41"/>
       <c r="F48" s="41" t="s">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H48" s="7">
         <v>2023</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B49" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C49" s="42" t="s">
-        <v>135</v>
-      </c>
-      <c r="D49" s="41" t="s">
-        <v>136</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D49" s="42"/>
       <c r="E49" s="41"/>
-      <c r="F49" s="41" t="s">
-        <v>104</v>
-      </c>
-      <c r="G49" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="F49" s="41"/>
+      <c r="G49" s="41"/>
       <c r="H49" s="7">
         <v>2023</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A50" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B50" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C50" s="42" t="s">
-        <v>137</v>
-      </c>
-      <c r="D50" s="41" t="s">
-        <v>138</v>
-      </c>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A50" s="14"/>
+      <c r="B50" s="15"/>
+      <c r="D50" s="42"/>
       <c r="E50" s="41"/>
-      <c r="F50" s="41" t="s">
-        <v>104</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="F50" s="41"/>
+      <c r="G50" s="41"/>
       <c r="H50" s="7">
         <v>2020</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A51" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B51" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C51" s="42" t="s">
-        <v>139</v>
-      </c>
-      <c r="D51" s="41" t="s">
-        <v>141</v>
-      </c>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A51" s="14"/>
+      <c r="B51" s="15"/>
+      <c r="D51" s="42"/>
       <c r="E51" s="41"/>
-      <c r="F51" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="G51" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="F51" s="41"/>
+      <c r="G51" s="41"/>
       <c r="H51" s="7">
         <v>2019</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A52" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B52" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C52" s="42" t="s">
-        <v>140</v>
-      </c>
-      <c r="D52" s="41" t="s">
-        <v>142</v>
-      </c>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52" s="14"/>
+      <c r="B52" s="15"/>
+      <c r="D52" s="42"/>
       <c r="E52" s="41"/>
-      <c r="F52" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="F52" s="41"/>
+      <c r="G52" s="41"/>
       <c r="H52" s="7">
         <v>2019</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A53" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B53" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C53" s="42" t="s">
-        <v>144</v>
-      </c>
-      <c r="D53" s="41" t="s">
-        <v>145</v>
-      </c>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A53" s="14"/>
+      <c r="B53" s="15"/>
+      <c r="D53" s="42"/>
       <c r="E53" s="41"/>
-      <c r="F53" s="41" t="s">
-        <v>146</v>
-      </c>
-      <c r="G53" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="F53" s="41"/>
+      <c r="G53" s="41"/>
       <c r="H53" s="7">
         <v>2019</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A54" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B54" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C54" s="42" t="s">
-        <v>147</v>
-      </c>
-      <c r="D54" s="41" t="s">
-        <v>148</v>
-      </c>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A54" s="14"/>
+      <c r="B54" s="15"/>
+      <c r="D54" s="42"/>
       <c r="E54" s="41"/>
-      <c r="F54" s="41" t="s">
-        <v>146</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="F54" s="41"/>
+      <c r="G54" s="41"/>
       <c r="H54" s="7">
         <v>2020</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A55" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B55" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C55" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="D55" s="41" t="s">
-        <v>150</v>
-      </c>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A55" s="14"/>
+      <c r="B55" s="15"/>
+      <c r="D55" s="42"/>
       <c r="E55" s="41"/>
-      <c r="F55" s="41" t="s">
-        <v>151</v>
-      </c>
-      <c r="G55" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="F55" s="41"/>
+      <c r="G55" s="41"/>
       <c r="H55" s="7">
         <v>2019</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A56" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B56" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C56" s="42" t="s">
-        <v>152</v>
-      </c>
-      <c r="D56" s="41" t="s">
-        <v>153</v>
-      </c>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A56" s="14"/>
+      <c r="B56" s="15"/>
+      <c r="D56" s="42"/>
       <c r="E56" s="41"/>
-      <c r="F56" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="G56" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="F56" s="41"/>
+      <c r="G56" s="41"/>
       <c r="H56" s="7">
         <v>2023</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A57" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="B57" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C57" s="42" t="s">
-        <v>154</v>
-      </c>
-      <c r="D57" s="41" t="s">
-        <v>155</v>
-      </c>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57" s="14"/>
+      <c r="B57" s="15"/>
+      <c r="D57" s="14"/>
       <c r="E57" s="41"/>
-      <c r="F57" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="G57" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="F57" s="41"/>
+      <c r="G57" s="41"/>
       <c r="H57" s="7">
         <v>2019</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A58" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C58" s="42" t="s">
-        <v>169</v>
-      </c>
-      <c r="D58" s="41" t="s">
-        <v>170</v>
-      </c>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A58" s="14"/>
+      <c r="B58" s="15"/>
+      <c r="D58" s="42"/>
       <c r="E58" s="41"/>
-      <c r="F58" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="G58" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="F58" s="41"/>
+      <c r="G58" s="41"/>
       <c r="H58" s="7">
         <v>2025</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A59" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C59" s="42" t="s">
-        <v>171</v>
-      </c>
-      <c r="D59" s="41" t="s">
-        <v>172</v>
-      </c>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A59" s="14"/>
+      <c r="B59" s="15"/>
+      <c r="D59" s="42"/>
       <c r="E59" s="41"/>
-      <c r="F59" s="41" t="s">
-        <v>173</v>
-      </c>
-      <c r="G59" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="F59" s="41"/>
+      <c r="G59" s="41"/>
       <c r="H59" s="7">
         <v>2026</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A60" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C60" s="42" t="s">
-        <v>38</v>
-      </c>
-      <c r="D60" s="41" t="s">
-        <v>174</v>
-      </c>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A60" s="14"/>
+      <c r="B60" s="15"/>
+      <c r="D60" s="42"/>
       <c r="E60" s="41"/>
-      <c r="F60" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="F60" s="41"/>
+      <c r="G60" s="41"/>
       <c r="H60" s="7">
         <v>2026</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A61" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C61" s="42" t="s">
-        <v>175</v>
-      </c>
-      <c r="D61" s="41" t="s">
-        <v>176</v>
-      </c>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A61" s="14"/>
+      <c r="B61" s="15"/>
+      <c r="D61" s="42"/>
       <c r="E61" s="41"/>
-      <c r="F61" s="41" t="s">
-        <v>90</v>
-      </c>
-      <c r="G61" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="F61" s="41"/>
+      <c r="G61" s="41"/>
       <c r="H61" s="7">
         <v>2026</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A62" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C62" s="42" t="s">
-        <v>33</v>
-      </c>
-      <c r="D62" s="41" t="s">
-        <v>32</v>
-      </c>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A62" s="14"/>
+      <c r="B62" s="15"/>
+      <c r="D62" s="42"/>
       <c r="E62" s="41"/>
-      <c r="F62" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="G62" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="F62" s="41"/>
+      <c r="G62" s="41"/>
       <c r="H62" s="7">
         <v>2026</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A63" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C63" s="42" t="s">
-        <v>177</v>
-      </c>
-      <c r="D63" s="41" t="s">
-        <v>86</v>
-      </c>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A63" s="14"/>
+      <c r="B63" s="15"/>
+      <c r="D63" s="42"/>
       <c r="E63" s="41"/>
-      <c r="F63" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="G63" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="F63" s="41"/>
+      <c r="G63" s="41"/>
       <c r="H63" s="7">
         <v>2026</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A64" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C64" s="42" t="s">
-        <v>179</v>
-      </c>
-      <c r="D64" s="41" t="s">
-        <v>32</v>
-      </c>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A64" s="14"/>
+      <c r="B64" s="15"/>
+      <c r="D64" s="42"/>
       <c r="E64" s="41"/>
-      <c r="F64" s="41" t="s">
-        <v>178</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="F64" s="41"/>
+      <c r="G64" s="41"/>
       <c r="H64" s="7">
         <v>2026</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A65" s="4"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="42"/>
-      <c r="D65" s="41"/>
+    <row r="65" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="14"/>
+      <c r="B65" s="15"/>
+      <c r="D65" s="42"/>
       <c r="E65" s="41"/>
       <c r="F65" s="41"/>
-      <c r="G65" s="6"/>
+      <c r="G65" s="41"/>
       <c r="H65" s="7"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A66" s="4"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="42"/>
-      <c r="D66" s="41"/>
+      <c r="A66" s="14"/>
+      <c r="B66" s="15"/>
+      <c r="D66" s="42"/>
       <c r="E66" s="41"/>
       <c r="F66" s="41"/>
-      <c r="G66" s="6"/>
+      <c r="G66" s="41"/>
       <c r="H66" s="7"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="4"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="42"/>
-      <c r="D67" s="41"/>
+      <c r="B67" s="15"/>
+      <c r="D67" s="42"/>
       <c r="E67" s="41"/>
       <c r="F67" s="41"/>
-      <c r="G67" s="6"/>
+      <c r="G67" s="41"/>
       <c r="H67" s="7"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="4"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="42"/>
-      <c r="D68" s="41"/>
+      <c r="B68" s="15"/>
+      <c r="D68" s="42"/>
       <c r="E68" s="41"/>
       <c r="F68" s="41"/>
-      <c r="G68" s="6"/>
+      <c r="G68" s="41"/>
       <c r="H68" s="7"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="4"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="42"/>
-      <c r="D69" s="41"/>
+      <c r="B69" s="15"/>
+      <c r="D69" s="42"/>
       <c r="E69" s="41"/>
       <c r="F69" s="41"/>
-      <c r="G69" s="6"/>
+      <c r="G69" s="41"/>
       <c r="H69" s="7"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="4"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="42"/>
-      <c r="D70" s="41"/>
+      <c r="B70" s="15"/>
+      <c r="D70" s="42"/>
       <c r="E70" s="41"/>
       <c r="F70" s="41"/>
-      <c r="G70" s="6"/>
+      <c r="G70" s="41"/>
       <c r="H70" s="7"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="4"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="42"/>
-      <c r="D71" s="41"/>
+      <c r="B71" s="15"/>
+      <c r="D71" s="42"/>
       <c r="E71" s="41"/>
       <c r="F71" s="41"/>
-      <c r="G71" s="6"/>
+      <c r="G71" s="41"/>
       <c r="H71" s="7"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="4"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="42"/>
-      <c r="D72" s="41"/>
+      <c r="B72" s="15"/>
+      <c r="D72" s="42"/>
       <c r="E72" s="41"/>
       <c r="F72" s="41"/>
-      <c r="G72" s="6"/>
+      <c r="G72" s="41"/>
       <c r="H72" s="7"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="4"/>
-      <c r="B73" s="5"/>
-      <c r="C73" s="42"/>
-      <c r="D73" s="41"/>
+      <c r="B73" s="15"/>
+      <c r="D73" s="42"/>
       <c r="E73" s="41"/>
       <c r="F73" s="41"/>
-      <c r="G73" s="6"/>
+      <c r="G73" s="41"/>
       <c r="H73" s="7"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="4"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="42"/>
-      <c r="D74" s="41"/>
+      <c r="B74" s="15"/>
+      <c r="D74" s="42"/>
       <c r="E74" s="41"/>
       <c r="F74" s="41"/>
-      <c r="G74" s="6"/>
+      <c r="G74" s="41"/>
       <c r="H74" s="7"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="4"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="42"/>
-      <c r="D75" s="41"/>
+      <c r="B75" s="15"/>
+      <c r="D75" s="42"/>
       <c r="E75" s="41"/>
       <c r="F75" s="41"/>
-      <c r="G75" s="6"/>
+      <c r="G75" s="41"/>
       <c r="H75" s="7"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="4"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="42"/>
-      <c r="D76" s="41"/>
+      <c r="B76" s="15"/>
+      <c r="D76" s="42"/>
       <c r="E76" s="41"/>
       <c r="F76" s="41"/>
-      <c r="G76" s="6"/>
+      <c r="G76" s="41"/>
       <c r="H76" s="7"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="4"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="42"/>
-      <c r="D77" s="41"/>
+      <c r="B77" s="15"/>
+      <c r="D77" s="42"/>
       <c r="E77" s="41"/>
       <c r="F77" s="41"/>
-      <c r="G77" s="6"/>
+      <c r="G77" s="41"/>
       <c r="H77" s="7"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="4"/>
-      <c r="B78" s="5"/>
-      <c r="C78" s="42"/>
-      <c r="D78" s="41"/>
+      <c r="B78" s="15"/>
+      <c r="D78" s="42"/>
       <c r="E78" s="41"/>
       <c r="F78" s="41"/>
-      <c r="G78" s="6"/>
+      <c r="G78" s="41"/>
       <c r="H78" s="7"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="4"/>
-      <c r="B79" s="5"/>
-      <c r="C79" s="42"/>
-      <c r="D79" s="41"/>
+      <c r="B79" s="15"/>
+      <c r="D79" s="42"/>
       <c r="E79" s="41"/>
       <c r="F79" s="41"/>
-      <c r="G79" s="6"/>
+      <c r="G79" s="41"/>
       <c r="H79" s="7"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="4"/>
-      <c r="B80" s="5"/>
-      <c r="C80" s="42"/>
-      <c r="D80" s="41"/>
+      <c r="B80" s="15"/>
+      <c r="D80" s="42"/>
       <c r="E80" s="41"/>
       <c r="F80" s="41"/>
-      <c r="G80" s="6"/>
+      <c r="G80" s="41"/>
       <c r="H80" s="7"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="4"/>
-      <c r="B81" s="5"/>
-      <c r="C81" s="42"/>
-      <c r="D81" s="41"/>
+      <c r="B81" s="15"/>
+      <c r="D81" s="42"/>
       <c r="E81" s="41"/>
       <c r="F81" s="41"/>
-      <c r="G81" s="6"/>
+      <c r="G81" s="41"/>
       <c r="H81" s="7"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="4"/>
-      <c r="B82" s="5"/>
-      <c r="C82" s="42"/>
-      <c r="D82" s="41"/>
+      <c r="B82" s="15"/>
+      <c r="D82" s="42"/>
       <c r="E82" s="41"/>
       <c r="F82" s="41"/>
-      <c r="G82" s="6"/>
+      <c r="G82" s="41"/>
       <c r="H82" s="7"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="4"/>
-      <c r="B83" s="5"/>
-      <c r="C83" s="42"/>
-      <c r="D83" s="41"/>
+      <c r="B83" s="15"/>
+      <c r="D83" s="42"/>
       <c r="E83" s="41"/>
       <c r="F83" s="41"/>
-      <c r="G83" s="6"/>
+      <c r="G83" s="41"/>
       <c r="H83" s="7"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="4"/>
-      <c r="B84" s="5"/>
-      <c r="C84" s="42"/>
-      <c r="D84" s="41"/>
+      <c r="B84" s="15"/>
+      <c r="D84" s="42"/>
       <c r="E84" s="41"/>
       <c r="F84" s="41"/>
-      <c r="G84" s="6"/>
+      <c r="G84" s="41"/>
       <c r="H84" s="7"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="4"/>
-      <c r="B85" s="5"/>
-      <c r="C85" s="42"/>
-      <c r="D85" s="41"/>
+      <c r="B85" s="15"/>
+      <c r="D85" s="42"/>
       <c r="E85" s="41"/>
       <c r="F85" s="41"/>
-      <c r="G85" s="6"/>
+      <c r="G85" s="41"/>
       <c r="H85" s="7"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="4"/>
-      <c r="B86" s="5"/>
-      <c r="C86" s="42"/>
-      <c r="D86" s="41"/>
+      <c r="B86" s="15"/>
+      <c r="D86" s="42"/>
       <c r="E86" s="41"/>
       <c r="F86" s="41"/>
-      <c r="G86" s="6"/>
+      <c r="G86" s="41"/>
       <c r="H86" s="7"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="4"/>
-      <c r="B87" s="5"/>
-      <c r="C87" s="42"/>
-      <c r="D87" s="41"/>
+      <c r="B87" s="15"/>
+      <c r="D87" s="42"/>
       <c r="E87" s="41"/>
       <c r="F87" s="41"/>
-      <c r="G87" s="6"/>
+      <c r="G87" s="41"/>
       <c r="H87" s="7"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="4"/>
-      <c r="B88" s="5"/>
-      <c r="C88" s="42"/>
-      <c r="D88" s="41"/>
+      <c r="B88" s="15"/>
+      <c r="D88" s="42"/>
       <c r="E88" s="41"/>
       <c r="F88" s="41"/>
-      <c r="G88" s="6"/>
+      <c r="G88" s="41"/>
       <c r="H88" s="7"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="4"/>
-      <c r="B89" s="5"/>
-      <c r="C89" s="42"/>
-      <c r="D89" s="41"/>
+      <c r="B89" s="15"/>
+      <c r="D89" s="42"/>
       <c r="E89" s="41"/>
       <c r="F89" s="41"/>
-      <c r="G89" s="6"/>
+      <c r="G89" s="41"/>
       <c r="H89" s="7"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="4"/>
-      <c r="B90" s="5"/>
-      <c r="C90" s="42"/>
-      <c r="D90" s="41"/>
+      <c r="B90" s="15"/>
+      <c r="D90" s="42"/>
       <c r="E90" s="41"/>
       <c r="F90" s="41"/>
-      <c r="G90" s="6"/>
+      <c r="G90" s="41"/>
       <c r="H90" s="7"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="4"/>
-      <c r="B91" s="5"/>
-      <c r="C91" s="42"/>
-      <c r="D91" s="41"/>
+      <c r="B91" s="15"/>
+      <c r="D91" s="42"/>
       <c r="E91" s="41"/>
       <c r="F91" s="41"/>
-      <c r="G91" s="6"/>
+      <c r="G91" s="41"/>
       <c r="H91" s="7"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="4"/>
-      <c r="B92" s="5"/>
-      <c r="C92" s="42"/>
-      <c r="D92" s="41"/>
+      <c r="B92" s="15"/>
+      <c r="D92" s="42"/>
       <c r="E92" s="41"/>
       <c r="F92" s="41"/>
-      <c r="G92" s="6"/>
+      <c r="G92" s="41"/>
       <c r="H92" s="7"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="4"/>
-      <c r="B93" s="5"/>
-      <c r="C93" s="42"/>
-      <c r="D93" s="41"/>
+      <c r="B93" s="15"/>
+      <c r="D93" s="42"/>
       <c r="E93" s="41"/>
       <c r="F93" s="41"/>
-      <c r="G93" s="6"/>
+      <c r="G93" s="41"/>
       <c r="H93" s="7"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="4"/>
-      <c r="B94" s="5"/>
-      <c r="C94" s="42"/>
-      <c r="D94" s="41"/>
+      <c r="B94" s="15"/>
+      <c r="D94" s="42"/>
       <c r="E94" s="41"/>
       <c r="F94" s="41"/>
-      <c r="G94" s="6"/>
+      <c r="G94" s="41"/>
       <c r="H94" s="7"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="4"/>
-      <c r="B95" s="5"/>
-      <c r="C95" s="42"/>
-      <c r="D95" s="41"/>
+      <c r="B95" s="15"/>
+      <c r="D95" s="42"/>
       <c r="E95" s="41"/>
       <c r="F95" s="41"/>
-      <c r="G95" s="6"/>
+      <c r="G95" s="41"/>
       <c r="H95" s="7"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="4"/>
-      <c r="B96" s="5"/>
-      <c r="C96" s="42"/>
-      <c r="D96" s="41"/>
+      <c r="B96" s="15"/>
+      <c r="D96" s="42"/>
       <c r="E96" s="41"/>
       <c r="F96" s="41"/>
-      <c r="G96" s="6"/>
+      <c r="G96" s="41"/>
       <c r="H96" s="7"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="4"/>
-      <c r="B97" s="5"/>
-      <c r="C97" s="42"/>
-      <c r="D97" s="41"/>
+      <c r="B97" s="15"/>
+      <c r="D97" s="42"/>
       <c r="E97" s="41"/>
       <c r="F97" s="41"/>
-      <c r="G97" s="6"/>
+      <c r="G97" s="41"/>
       <c r="H97" s="7"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="4"/>
-      <c r="B98" s="5"/>
-      <c r="C98" s="42"/>
-      <c r="D98" s="41"/>
+      <c r="B98" s="15"/>
+      <c r="D98" s="42"/>
       <c r="E98" s="41"/>
       <c r="F98" s="41"/>
-      <c r="G98" s="6"/>
+      <c r="G98" s="41"/>
       <c r="H98" s="7"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="4"/>
-      <c r="B99" s="5"/>
-      <c r="C99" s="42"/>
-      <c r="D99" s="41"/>
+      <c r="B99" s="15"/>
+      <c r="D99" s="42"/>
       <c r="E99" s="41"/>
       <c r="F99" s="41"/>
-      <c r="G99" s="6"/>
+      <c r="G99" s="41"/>
       <c r="H99" s="7"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="4"/>
-      <c r="B100" s="5"/>
-      <c r="C100" s="42"/>
-      <c r="D100" s="41"/>
+      <c r="B100" s="15"/>
+      <c r="D100" s="42"/>
       <c r="E100" s="41"/>
       <c r="F100" s="41"/>
-      <c r="G100" s="6"/>
+      <c r="G100" s="41"/>
       <c r="H100" s="7"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="4"/>
-      <c r="B101" s="5"/>
-      <c r="C101" s="42"/>
-      <c r="D101" s="41"/>
+      <c r="B101" s="15"/>
+      <c r="D101" s="42"/>
       <c r="E101" s="41"/>
       <c r="F101" s="41"/>
-      <c r="G101" s="6"/>
+      <c r="G101" s="41"/>
       <c r="H101" s="7"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="4"/>
-      <c r="B102" s="5"/>
-      <c r="C102" s="42"/>
-      <c r="D102" s="41"/>
+      <c r="B102" s="15"/>
+      <c r="D102" s="42"/>
       <c r="E102" s="41"/>
       <c r="F102" s="41"/>
-      <c r="G102" s="6"/>
+      <c r="G102" s="41"/>
       <c r="H102" s="7"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="4"/>
-      <c r="B103" s="5"/>
-      <c r="C103" s="42"/>
-      <c r="D103" s="41"/>
+      <c r="B103" s="15"/>
+      <c r="D103" s="42"/>
       <c r="E103" s="41"/>
       <c r="F103" s="41"/>
-      <c r="G103" s="6"/>
+      <c r="G103" s="41"/>
       <c r="H103" s="7"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="4"/>
-      <c r="B104" s="5"/>
-      <c r="C104" s="42"/>
-      <c r="D104" s="41"/>
+      <c r="B104" s="15"/>
+      <c r="D104" s="42"/>
       <c r="E104" s="41"/>
       <c r="F104" s="41"/>
-      <c r="G104" s="6"/>
+      <c r="G104" s="41"/>
       <c r="H104" s="7"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="4"/>
-      <c r="B105" s="5"/>
-      <c r="C105" s="42"/>
-      <c r="D105" s="41"/>
+      <c r="B105" s="15"/>
+      <c r="D105" s="42"/>
       <c r="E105" s="41"/>
       <c r="F105" s="41"/>
-      <c r="G105" s="6"/>
+      <c r="G105" s="41"/>
       <c r="H105" s="7"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="4"/>
-      <c r="B106" s="5"/>
-      <c r="C106" s="42"/>
-      <c r="D106" s="41"/>
+      <c r="B106" s="15"/>
+      <c r="D106" s="42"/>
       <c r="E106" s="41"/>
       <c r="F106" s="41"/>
-      <c r="G106" s="6"/>
+      <c r="G106" s="41"/>
       <c r="H106" s="7"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="4"/>
-      <c r="B107" s="5"/>
-      <c r="C107" s="42"/>
-      <c r="D107" s="41"/>
+      <c r="B107" s="15"/>
+      <c r="D107" s="42"/>
       <c r="E107" s="41"/>
       <c r="F107" s="41"/>
-      <c r="G107" s="6"/>
+      <c r="G107" s="41"/>
       <c r="H107" s="7"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="4"/>
-      <c r="B108" s="5"/>
-      <c r="C108" s="42"/>
-      <c r="D108" s="41"/>
+      <c r="B108" s="15"/>
+      <c r="D108" s="42"/>
       <c r="E108" s="41"/>
       <c r="F108" s="41"/>
-      <c r="G108" s="6"/>
+      <c r="G108" s="41"/>
       <c r="H108" s="7"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="4"/>
-      <c r="B109" s="5"/>
-      <c r="C109" s="42"/>
-      <c r="D109" s="41"/>
+      <c r="B109" s="15"/>
+      <c r="D109" s="42"/>
       <c r="E109" s="41"/>
       <c r="F109" s="41"/>
-      <c r="G109" s="6"/>
+      <c r="G109" s="41"/>
       <c r="H109" s="7"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="4"/>
-      <c r="B110" s="5"/>
-      <c r="C110" s="42"/>
-      <c r="D110" s="41"/>
+      <c r="B110" s="15"/>
+      <c r="D110" s="42"/>
       <c r="E110" s="41"/>
       <c r="F110" s="41"/>
-      <c r="G110" s="6"/>
+      <c r="G110" s="41"/>
       <c r="H110" s="7"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="4"/>
-      <c r="B111" s="5"/>
-      <c r="C111" s="42"/>
-      <c r="D111" s="41"/>
+      <c r="B111" s="15"/>
+      <c r="D111" s="42"/>
       <c r="E111" s="41"/>
       <c r="F111" s="41"/>
-      <c r="G111" s="6"/>
+      <c r="G111" s="41"/>
       <c r="H111" s="7"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="4"/>
-      <c r="B112" s="5"/>
-      <c r="C112" s="42"/>
-      <c r="D112" s="41"/>
+      <c r="B112" s="15"/>
+      <c r="D112" s="42"/>
       <c r="E112" s="41"/>
       <c r="F112" s="41"/>
-      <c r="G112" s="6"/>
+      <c r="G112" s="41"/>
       <c r="H112" s="7"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="4"/>
-      <c r="B113" s="5"/>
-      <c r="C113" s="42"/>
-      <c r="D113" s="41"/>
+      <c r="B113" s="15"/>
+      <c r="D113" s="42"/>
       <c r="E113" s="41"/>
       <c r="F113" s="41"/>
-      <c r="G113" s="6"/>
+      <c r="G113" s="41"/>
       <c r="H113" s="7"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="4"/>
-      <c r="B114" s="5"/>
-      <c r="C114" s="42"/>
-      <c r="D114" s="41"/>
+      <c r="B114" s="15"/>
+      <c r="D114" s="42"/>
       <c r="E114" s="41"/>
       <c r="F114" s="41"/>
-      <c r="G114" s="6"/>
+      <c r="G114" s="41"/>
       <c r="H114" s="7"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="4"/>
-      <c r="B115" s="5"/>
-      <c r="C115" s="42"/>
-      <c r="D115" s="41"/>
+      <c r="B115" s="15"/>
+      <c r="D115" s="42"/>
       <c r="E115" s="41"/>
       <c r="F115" s="41"/>
-      <c r="G115" s="6"/>
+      <c r="G115" s="41"/>
       <c r="H115" s="7"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="4"/>
-      <c r="B116" s="5"/>
-      <c r="C116" s="42"/>
-      <c r="D116" s="41"/>
+      <c r="B116" s="15"/>
+      <c r="D116" s="42"/>
       <c r="E116" s="41"/>
       <c r="F116" s="41"/>
-      <c r="G116" s="6"/>
+      <c r="G116" s="41"/>
       <c r="H116" s="7"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="4"/>
-      <c r="B117" s="5"/>
-      <c r="C117" s="42"/>
-      <c r="D117" s="41"/>
+      <c r="B117" s="15"/>
+      <c r="D117" s="42"/>
       <c r="E117" s="41"/>
       <c r="F117" s="41"/>
-      <c r="G117" s="6"/>
+      <c r="G117" s="41"/>
       <c r="H117" s="7"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="4"/>
-      <c r="B118" s="5"/>
-      <c r="C118" s="42"/>
-      <c r="D118" s="41"/>
+      <c r="B118" s="15"/>
+      <c r="D118" s="42"/>
       <c r="E118" s="41"/>
       <c r="F118" s="41"/>
-      <c r="G118" s="6"/>
+      <c r="G118" s="41"/>
       <c r="H118" s="7"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="4"/>
-      <c r="B119" s="5"/>
-      <c r="C119" s="42"/>
-      <c r="D119" s="41"/>
+      <c r="B119" s="15"/>
+      <c r="D119" s="42"/>
       <c r="E119" s="41"/>
       <c r="F119" s="41"/>
-      <c r="G119" s="6"/>
+      <c r="G119" s="41"/>
       <c r="H119" s="7"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="4"/>
-      <c r="B120" s="5"/>
-      <c r="C120" s="42"/>
-      <c r="D120" s="41"/>
+      <c r="B120" s="15"/>
+      <c r="D120" s="42"/>
       <c r="E120" s="41"/>
       <c r="F120" s="41"/>
-      <c r="G120" s="6"/>
+      <c r="G120" s="41"/>
       <c r="H120" s="7"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="4"/>
-      <c r="B121" s="5"/>
-      <c r="C121" s="42"/>
-      <c r="D121" s="41"/>
+      <c r="B121" s="15"/>
+      <c r="D121" s="42"/>
       <c r="E121" s="41"/>
       <c r="F121" s="41"/>
-      <c r="G121" s="6"/>
+      <c r="G121" s="41"/>
       <c r="H121" s="7"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="4"/>
-      <c r="B122" s="5"/>
-      <c r="C122" s="42"/>
-      <c r="D122" s="41"/>
+      <c r="B122" s="15"/>
+      <c r="D122" s="42"/>
       <c r="E122" s="41"/>
       <c r="F122" s="41"/>
-      <c r="G122" s="6"/>
+      <c r="G122" s="41"/>
       <c r="H122" s="7"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="4"/>
-      <c r="B123" s="5"/>
-      <c r="C123" s="42"/>
-      <c r="D123" s="41"/>
+      <c r="B123" s="15"/>
+      <c r="D123" s="42"/>
       <c r="E123" s="41"/>
       <c r="F123" s="41"/>
-      <c r="G123" s="6"/>
+      <c r="G123" s="41"/>
       <c r="H123" s="7"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="4"/>
-      <c r="B124" s="5"/>
+      <c r="B124" s="15"/>
       <c r="C124" s="42"/>
       <c r="D124" s="41"/>
       <c r="E124" s="41"/>
@@ -3953,7 +3634,7 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="4"/>
-      <c r="B125" s="5"/>
+      <c r="B125" s="15"/>
       <c r="C125" s="42"/>
       <c r="D125" s="41"/>
       <c r="E125" s="41"/>
@@ -3963,7 +3644,7 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="4"/>
-      <c r="B126" s="5"/>
+      <c r="B126" s="15"/>
       <c r="C126" s="42"/>
       <c r="D126" s="41"/>
       <c r="E126" s="41"/>
@@ -3973,7 +3654,7 @@
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="4"/>
-      <c r="B127" s="5"/>
+      <c r="B127" s="15"/>
       <c r="C127" s="42"/>
       <c r="D127" s="41"/>
       <c r="E127" s="41"/>
@@ -3983,7 +3664,7 @@
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="4"/>
-      <c r="B128" s="5"/>
+      <c r="B128" s="15"/>
       <c r="C128" s="42"/>
       <c r="D128" s="41"/>
       <c r="E128" s="41"/>
@@ -3993,7 +3674,7 @@
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="4"/>
-      <c r="B129" s="5"/>
+      <c r="B129" s="15"/>
       <c r="C129" s="42"/>
       <c r="D129" s="41"/>
       <c r="E129" s="41"/>
@@ -4003,7 +3684,7 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="4"/>
-      <c r="B130" s="5"/>
+      <c r="B130" s="15"/>
       <c r="C130" s="42"/>
       <c r="D130" s="41"/>
       <c r="E130" s="41"/>
@@ -4013,7 +3694,7 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="4"/>
-      <c r="B131" s="5"/>
+      <c r="B131" s="15"/>
       <c r="C131" s="42"/>
       <c r="D131" s="41"/>
       <c r="E131" s="41"/>
@@ -4023,7 +3704,7 @@
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="4"/>
-      <c r="B132" s="5"/>
+      <c r="B132" s="15"/>
       <c r="C132" s="42"/>
       <c r="D132" s="41"/>
       <c r="E132" s="41"/>
@@ -4033,7 +3714,7 @@
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="4"/>
-      <c r="B133" s="5"/>
+      <c r="B133" s="15"/>
       <c r="C133" s="42"/>
       <c r="D133" s="41"/>
       <c r="E133" s="41"/>
@@ -4043,7 +3724,7 @@
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="4"/>
-      <c r="B134" s="5"/>
+      <c r="B134" s="15"/>
       <c r="C134" s="42"/>
       <c r="D134" s="41"/>
       <c r="E134" s="41"/>
@@ -4053,7 +3734,7 @@
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="4"/>
-      <c r="B135" s="5"/>
+      <c r="B135" s="15"/>
       <c r="C135" s="42"/>
       <c r="D135" s="41"/>
       <c r="E135" s="41"/>
@@ -4063,7 +3744,7 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="4"/>
-      <c r="B136" s="5"/>
+      <c r="B136" s="15"/>
       <c r="C136" s="42"/>
       <c r="D136" s="41"/>
       <c r="E136" s="41"/>
@@ -4073,7 +3754,7 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="4"/>
-      <c r="B137" s="5"/>
+      <c r="B137" s="15"/>
       <c r="C137" s="42"/>
       <c r="D137" s="41"/>
       <c r="E137" s="41"/>
@@ -4083,7 +3764,7 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="4"/>
-      <c r="B138" s="5"/>
+      <c r="B138" s="15"/>
       <c r="C138" s="42"/>
       <c r="D138" s="41"/>
       <c r="E138" s="41"/>
@@ -4093,7 +3774,7 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="4"/>
-      <c r="B139" s="5"/>
+      <c r="B139" s="15"/>
       <c r="C139" s="42"/>
       <c r="D139" s="41"/>
       <c r="E139" s="41"/>
@@ -4103,7 +3784,7 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="4"/>
-      <c r="B140" s="5"/>
+      <c r="B140" s="15"/>
       <c r="C140" s="42"/>
       <c r="D140" s="41"/>
       <c r="E140" s="41"/>
@@ -4113,7 +3794,7 @@
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="4"/>
-      <c r="B141" s="5"/>
+      <c r="B141" s="15"/>
       <c r="C141" s="42"/>
       <c r="D141" s="41"/>
       <c r="E141" s="41"/>
@@ -4123,7 +3804,7 @@
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="4"/>
-      <c r="B142" s="5"/>
+      <c r="B142" s="15"/>
       <c r="C142" s="42"/>
       <c r="D142" s="41"/>
       <c r="E142" s="41"/>
@@ -4133,7 +3814,7 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="4"/>
-      <c r="B143" s="5"/>
+      <c r="B143" s="15"/>
       <c r="C143" s="42"/>
       <c r="D143" s="41"/>
       <c r="E143" s="41"/>
@@ -4143,7 +3824,7 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="4"/>
-      <c r="B144" s="5"/>
+      <c r="B144" s="15"/>
       <c r="C144" s="42"/>
       <c r="D144" s="41"/>
       <c r="E144" s="41"/>
@@ -4153,7 +3834,7 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="4"/>
-      <c r="B145" s="5"/>
+      <c r="B145" s="15"/>
       <c r="C145" s="42"/>
       <c r="D145" s="41"/>
       <c r="E145" s="41"/>
@@ -4163,7 +3844,7 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="4"/>
-      <c r="B146" s="5"/>
+      <c r="B146" s="15"/>
       <c r="C146" s="42"/>
       <c r="D146" s="41"/>
       <c r="E146" s="41"/>
@@ -4173,7 +3854,7 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="4"/>
-      <c r="B147" s="5"/>
+      <c r="B147" s="15"/>
       <c r="C147" s="42"/>
       <c r="D147" s="41"/>
       <c r="E147" s="41"/>
@@ -4183,7 +3864,7 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="4"/>
-      <c r="B148" s="5"/>
+      <c r="B148" s="15"/>
       <c r="C148" s="42"/>
       <c r="D148" s="41"/>
       <c r="E148" s="41"/>
@@ -4193,7 +3874,7 @@
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="4"/>
-      <c r="B149" s="5"/>
+      <c r="B149" s="15"/>
       <c r="C149" s="42"/>
       <c r="D149" s="41"/>
       <c r="E149" s="41"/>
@@ -4203,7 +3884,7 @@
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="4"/>
-      <c r="B150" s="5"/>
+      <c r="B150" s="15"/>
       <c r="C150" s="42"/>
       <c r="D150" s="41"/>
       <c r="E150" s="41"/>
@@ -4213,7 +3894,7 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="4"/>
-      <c r="B151" s="5"/>
+      <c r="B151" s="15"/>
       <c r="C151" s="42"/>
       <c r="D151" s="41"/>
       <c r="E151" s="41"/>
@@ -4223,7 +3904,7 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="4"/>
-      <c r="B152" s="5"/>
+      <c r="B152" s="15"/>
       <c r="C152" s="42"/>
       <c r="D152" s="41"/>
       <c r="E152" s="41"/>
@@ -4233,7 +3914,7 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="4"/>
-      <c r="B153" s="5"/>
+      <c r="B153" s="15"/>
       <c r="C153" s="42"/>
       <c r="D153" s="41"/>
       <c r="E153" s="41"/>
@@ -4243,7 +3924,7 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="4"/>
-      <c r="B154" s="5"/>
+      <c r="B154" s="15"/>
       <c r="C154" s="42"/>
       <c r="D154" s="41"/>
       <c r="E154" s="41"/>
@@ -4253,7 +3934,7 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="4"/>
-      <c r="B155" s="5"/>
+      <c r="B155" s="15"/>
       <c r="C155" s="42"/>
       <c r="D155" s="41"/>
       <c r="E155" s="41"/>
@@ -4263,7 +3944,7 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="4"/>
-      <c r="B156" s="5"/>
+      <c r="B156" s="15"/>
       <c r="C156" s="42"/>
       <c r="D156" s="41"/>
       <c r="E156" s="41"/>
@@ -4273,7 +3954,7 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="4"/>
-      <c r="B157" s="5"/>
+      <c r="B157" s="15"/>
       <c r="C157" s="42"/>
       <c r="D157" s="41"/>
       <c r="E157" s="41"/>
@@ -4283,7 +3964,7 @@
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="4"/>
-      <c r="B158" s="5"/>
+      <c r="B158" s="15"/>
       <c r="C158" s="42"/>
       <c r="D158" s="41"/>
       <c r="E158" s="41"/>
@@ -4293,7 +3974,7 @@
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="4"/>
-      <c r="B159" s="5"/>
+      <c r="B159" s="15"/>
       <c r="C159" s="42"/>
       <c r="D159" s="41"/>
       <c r="E159" s="41"/>
@@ -4303,7 +3984,7 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="4"/>
-      <c r="B160" s="5"/>
+      <c r="B160" s="15"/>
       <c r="C160" s="42"/>
       <c r="D160" s="41"/>
       <c r="E160" s="41"/>
@@ -4313,7 +3994,7 @@
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="4"/>
-      <c r="B161" s="5"/>
+      <c r="B161" s="15"/>
       <c r="C161" s="42"/>
       <c r="D161" s="41"/>
       <c r="E161" s="41"/>
@@ -4323,7 +4004,7 @@
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="4"/>
-      <c r="B162" s="5"/>
+      <c r="B162" s="15"/>
       <c r="C162" s="42"/>
       <c r="D162" s="41"/>
       <c r="E162" s="41"/>
@@ -4333,7 +4014,7 @@
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="4"/>
-      <c r="B163" s="5"/>
+      <c r="B163" s="15"/>
       <c r="C163" s="42"/>
       <c r="D163" s="41"/>
       <c r="E163" s="41"/>
@@ -4343,7 +4024,7 @@
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="4"/>
-      <c r="B164" s="5"/>
+      <c r="B164" s="15"/>
       <c r="C164" s="42"/>
       <c r="D164" s="41"/>
       <c r="E164" s="41"/>
@@ -4353,7 +4034,7 @@
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="4"/>
-      <c r="B165" s="5"/>
+      <c r="B165" s="15"/>
       <c r="C165" s="42"/>
       <c r="D165" s="41"/>
       <c r="E165" s="41"/>
@@ -4363,7 +4044,7 @@
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="4"/>
-      <c r="B166" s="5"/>
+      <c r="B166" s="15"/>
       <c r="C166" s="42"/>
       <c r="D166" s="41"/>
       <c r="E166" s="41"/>
@@ -4373,7 +4054,7 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="4"/>
-      <c r="B167" s="5"/>
+      <c r="B167" s="15"/>
       <c r="C167" s="42"/>
       <c r="D167" s="41"/>
       <c r="E167" s="41"/>
@@ -4383,7 +4064,7 @@
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="4"/>
-      <c r="B168" s="5"/>
+      <c r="B168" s="15"/>
       <c r="C168" s="42"/>
       <c r="D168" s="41"/>
       <c r="E168" s="41"/>
@@ -4393,7 +4074,7 @@
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="4"/>
-      <c r="B169" s="5"/>
+      <c r="B169" s="15"/>
       <c r="C169" s="42"/>
       <c r="D169" s="41"/>
       <c r="E169" s="41"/>
@@ -4403,7 +4084,7 @@
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="4"/>
-      <c r="B170" s="5"/>
+      <c r="B170" s="15"/>
       <c r="C170" s="42"/>
       <c r="D170" s="41"/>
       <c r="E170" s="41"/>
@@ -4413,7 +4094,7 @@
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="4"/>
-      <c r="B171" s="5"/>
+      <c r="B171" s="15"/>
       <c r="C171" s="42"/>
       <c r="D171" s="41"/>
       <c r="E171" s="41"/>
@@ -4423,7 +4104,7 @@
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="4"/>
-      <c r="B172" s="5"/>
+      <c r="B172" s="15"/>
       <c r="C172" s="42"/>
       <c r="D172" s="41"/>
       <c r="E172" s="41"/>
@@ -4433,7 +4114,7 @@
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="4"/>
-      <c r="B173" s="5"/>
+      <c r="B173" s="15"/>
       <c r="C173" s="42"/>
       <c r="D173" s="41"/>
       <c r="E173" s="41"/>
@@ -4443,7 +4124,7 @@
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="4"/>
-      <c r="B174" s="5"/>
+      <c r="B174" s="15"/>
       <c r="C174" s="42"/>
       <c r="D174" s="41"/>
       <c r="E174" s="41"/>
@@ -4453,7 +4134,7 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="4"/>
-      <c r="B175" s="5"/>
+      <c r="B175" s="15"/>
       <c r="C175" s="42"/>
       <c r="D175" s="41"/>
       <c r="E175" s="41"/>
@@ -4463,7 +4144,7 @@
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="4"/>
-      <c r="B176" s="5"/>
+      <c r="B176" s="15"/>
       <c r="C176" s="42"/>
       <c r="D176" s="41"/>
       <c r="E176" s="41"/>
@@ -4473,7 +4154,7 @@
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="4"/>
-      <c r="B177" s="5"/>
+      <c r="B177" s="15"/>
       <c r="C177" s="42"/>
       <c r="D177" s="41"/>
       <c r="E177" s="41"/>
@@ -4483,7 +4164,7 @@
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="4"/>
-      <c r="B178" s="5"/>
+      <c r="B178" s="15"/>
       <c r="C178" s="42"/>
       <c r="D178" s="41"/>
       <c r="E178" s="41"/>
@@ -4493,7 +4174,7 @@
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="4"/>
-      <c r="B179" s="5"/>
+      <c r="B179" s="15"/>
       <c r="C179" s="42"/>
       <c r="D179" s="41"/>
       <c r="E179" s="41"/>
@@ -4503,7 +4184,7 @@
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="4"/>
-      <c r="B180" s="5"/>
+      <c r="B180" s="15"/>
       <c r="C180" s="42"/>
       <c r="D180" s="41"/>
       <c r="E180" s="41"/>
@@ -4513,7 +4194,7 @@
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="4"/>
-      <c r="B181" s="5"/>
+      <c r="B181" s="15"/>
       <c r="C181" s="42"/>
       <c r="D181" s="41"/>
       <c r="E181" s="41"/>
@@ -4523,7 +4204,7 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="4"/>
-      <c r="B182" s="5"/>
+      <c r="B182" s="15"/>
       <c r="C182" s="42"/>
       <c r="D182" s="41"/>
       <c r="E182" s="41"/>
@@ -4533,7 +4214,7 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" s="4"/>
-      <c r="B183" s="5"/>
+      <c r="B183" s="15"/>
       <c r="C183" s="42"/>
       <c r="D183" s="41"/>
       <c r="E183" s="41"/>
@@ -4543,7 +4224,7 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" s="4"/>
-      <c r="B184" s="5"/>
+      <c r="B184" s="15"/>
       <c r="C184" s="42"/>
       <c r="D184" s="41"/>
       <c r="E184" s="41"/>
@@ -4553,7 +4234,7 @@
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" s="4"/>
-      <c r="B185" s="5"/>
+      <c r="B185" s="15"/>
       <c r="C185" s="42"/>
       <c r="D185" s="41"/>
       <c r="E185" s="41"/>
@@ -4563,7 +4244,7 @@
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" s="4"/>
-      <c r="B186" s="5"/>
+      <c r="B186" s="15"/>
       <c r="C186" s="42"/>
       <c r="D186" s="41"/>
       <c r="E186" s="41"/>
@@ -4573,7 +4254,7 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" s="4"/>
-      <c r="B187" s="5"/>
+      <c r="B187" s="15"/>
       <c r="C187" s="42"/>
       <c r="D187" s="41"/>
       <c r="E187" s="41"/>
@@ -4583,7 +4264,7 @@
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="4"/>
-      <c r="B188" s="5"/>
+      <c r="B188" s="15"/>
       <c r="C188" s="42"/>
       <c r="D188" s="41"/>
       <c r="E188" s="41"/>
@@ -4593,7 +4274,7 @@
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" s="4"/>
-      <c r="B189" s="5"/>
+      <c r="B189" s="15"/>
       <c r="C189" s="42"/>
       <c r="D189" s="41"/>
       <c r="E189" s="41"/>
@@ -4603,7 +4284,7 @@
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="4"/>
-      <c r="B190" s="5"/>
+      <c r="B190" s="15"/>
       <c r="C190" s="42"/>
       <c r="D190" s="41"/>
       <c r="E190" s="41"/>
@@ -4613,7 +4294,7 @@
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" s="4"/>
-      <c r="B191" s="5"/>
+      <c r="B191" s="15"/>
       <c r="C191" s="42"/>
       <c r="D191" s="41"/>
       <c r="E191" s="41"/>
@@ -4623,7 +4304,7 @@
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" s="4"/>
-      <c r="B192" s="5"/>
+      <c r="B192" s="15"/>
       <c r="C192" s="42"/>
       <c r="D192" s="41"/>
       <c r="E192" s="41"/>
@@ -4633,7 +4314,7 @@
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="4"/>
-      <c r="B193" s="5"/>
+      <c r="B193" s="15"/>
       <c r="C193" s="42"/>
       <c r="D193" s="41"/>
       <c r="E193" s="41"/>
@@ -4643,7 +4324,7 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="4"/>
-      <c r="B194" s="5"/>
+      <c r="B194" s="15"/>
       <c r="C194" s="42"/>
       <c r="D194" s="41"/>
       <c r="E194" s="41"/>
@@ -4653,7 +4334,7 @@
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="4"/>
-      <c r="B195" s="5"/>
+      <c r="B195" s="15"/>
       <c r="C195" s="42"/>
       <c r="D195" s="41"/>
       <c r="E195" s="41"/>
@@ -4663,7 +4344,7 @@
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="4"/>
-      <c r="B196" s="5"/>
+      <c r="B196" s="15"/>
       <c r="C196" s="42"/>
       <c r="D196" s="41"/>
       <c r="E196" s="41"/>
@@ -4673,7 +4354,7 @@
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="4"/>
-      <c r="B197" s="5"/>
+      <c r="B197" s="15"/>
       <c r="C197" s="42"/>
       <c r="D197" s="41"/>
       <c r="E197" s="41"/>
@@ -4683,7 +4364,7 @@
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="4"/>
-      <c r="B198" s="5"/>
+      <c r="B198" s="15"/>
       <c r="C198" s="42"/>
       <c r="D198" s="41"/>
       <c r="E198" s="41"/>
@@ -4693,7 +4374,7 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="4"/>
-      <c r="B199" s="5"/>
+      <c r="B199" s="15"/>
       <c r="C199" s="42"/>
       <c r="D199" s="41"/>
       <c r="E199" s="41"/>
@@ -4703,7 +4384,7 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="4"/>
-      <c r="B200" s="5"/>
+      <c r="B200" s="15"/>
       <c r="C200" s="42"/>
       <c r="D200" s="41"/>
       <c r="E200" s="41"/>
@@ -4713,7 +4394,7 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="4"/>
-      <c r="B201" s="5"/>
+      <c r="B201" s="15"/>
       <c r="C201" s="42"/>
       <c r="D201" s="41"/>
       <c r="E201" s="41"/>
@@ -4723,7 +4404,7 @@
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="4"/>
-      <c r="B202" s="5"/>
+      <c r="B202" s="15"/>
       <c r="C202" s="42"/>
       <c r="D202" s="41"/>
       <c r="E202" s="41"/>
@@ -4733,7 +4414,7 @@
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="4"/>
-      <c r="B203" s="5"/>
+      <c r="B203" s="15"/>
       <c r="C203" s="42"/>
       <c r="D203" s="41"/>
       <c r="E203" s="41"/>
@@ -4743,7 +4424,7 @@
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="4"/>
-      <c r="B204" s="5"/>
+      <c r="B204" s="15"/>
       <c r="C204" s="42"/>
       <c r="D204" s="41"/>
       <c r="E204" s="41"/>
@@ -4753,7 +4434,7 @@
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="4"/>
-      <c r="B205" s="5"/>
+      <c r="B205" s="15"/>
       <c r="C205" s="42"/>
       <c r="D205" s="41"/>
       <c r="E205" s="41"/>
@@ -4763,7 +4444,7 @@
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="4"/>
-      <c r="B206" s="5"/>
+      <c r="B206" s="15"/>
       <c r="C206" s="42"/>
       <c r="D206" s="41"/>
       <c r="E206" s="41"/>
@@ -4773,7 +4454,7 @@
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="4"/>
-      <c r="B207" s="5"/>
+      <c r="B207" s="15"/>
       <c r="C207" s="42"/>
       <c r="D207" s="41"/>
       <c r="E207" s="41"/>
@@ -4783,7 +4464,7 @@
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="4"/>
-      <c r="B208" s="5"/>
+      <c r="B208" s="15"/>
       <c r="C208" s="42"/>
       <c r="D208" s="41"/>
       <c r="E208" s="41"/>
@@ -4793,7 +4474,7 @@
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="4"/>
-      <c r="B209" s="5"/>
+      <c r="B209" s="15"/>
       <c r="C209" s="42"/>
       <c r="D209" s="41"/>
       <c r="E209" s="41"/>
@@ -4803,7 +4484,7 @@
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="4"/>
-      <c r="B210" s="5"/>
+      <c r="B210" s="15"/>
       <c r="C210" s="42"/>
       <c r="D210" s="41"/>
       <c r="E210" s="41"/>
@@ -4813,7 +4494,7 @@
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" s="4"/>
-      <c r="B211" s="5"/>
+      <c r="B211" s="15"/>
       <c r="C211" s="42"/>
       <c r="D211" s="41"/>
       <c r="E211" s="41"/>
@@ -4823,7 +4504,7 @@
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" s="4"/>
-      <c r="B212" s="5"/>
+      <c r="B212" s="15"/>
       <c r="C212" s="42"/>
       <c r="D212" s="41"/>
       <c r="E212" s="41"/>
@@ -4833,7 +4514,7 @@
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="4"/>
-      <c r="B213" s="5"/>
+      <c r="B213" s="15"/>
       <c r="C213" s="42"/>
       <c r="D213" s="41"/>
       <c r="E213" s="41"/>
@@ -4843,7 +4524,7 @@
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="4"/>
-      <c r="B214" s="5"/>
+      <c r="B214" s="15"/>
       <c r="C214" s="42"/>
       <c r="D214" s="41"/>
       <c r="E214" s="41"/>
@@ -4853,7 +4534,7 @@
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="4"/>
-      <c r="B215" s="5"/>
+      <c r="B215" s="15"/>
       <c r="C215" s="42"/>
       <c r="D215" s="41"/>
       <c r="E215" s="41"/>
@@ -4863,7 +4544,7 @@
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="4"/>
-      <c r="B216" s="5"/>
+      <c r="B216" s="15"/>
       <c r="C216" s="42"/>
       <c r="D216" s="41"/>
       <c r="E216" s="41"/>
@@ -4873,7 +4554,7 @@
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="4"/>
-      <c r="B217" s="5"/>
+      <c r="B217" s="15"/>
       <c r="C217" s="42"/>
       <c r="D217" s="41"/>
       <c r="E217" s="41"/>
@@ -4883,7 +4564,7 @@
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="4"/>
-      <c r="B218" s="5"/>
+      <c r="B218" s="15"/>
       <c r="C218" s="42"/>
       <c r="D218" s="41"/>
       <c r="E218" s="41"/>
@@ -4893,7 +4574,7 @@
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="4"/>
-      <c r="B219" s="5"/>
+      <c r="B219" s="15"/>
       <c r="C219" s="42"/>
       <c r="D219" s="41"/>
       <c r="E219" s="41"/>
@@ -4903,7 +4584,7 @@
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="4"/>
-      <c r="B220" s="5"/>
+      <c r="B220" s="15"/>
       <c r="C220" s="42"/>
       <c r="D220" s="41"/>
       <c r="E220" s="41"/>
@@ -4913,7 +4594,7 @@
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="4"/>
-      <c r="B221" s="5"/>
+      <c r="B221" s="15"/>
       <c r="C221" s="42"/>
       <c r="D221" s="41"/>
       <c r="E221" s="41"/>
@@ -4923,7 +4604,7 @@
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="4"/>
-      <c r="B222" s="5"/>
+      <c r="B222" s="15"/>
       <c r="C222" s="42"/>
       <c r="D222" s="41"/>
       <c r="E222" s="41"/>
@@ -4933,7 +4614,7 @@
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" s="4"/>
-      <c r="B223" s="5"/>
+      <c r="B223" s="15"/>
       <c r="C223" s="42"/>
       <c r="D223" s="41"/>
       <c r="E223" s="41"/>
@@ -4943,7 +4624,7 @@
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="4"/>
-      <c r="B224" s="5"/>
+      <c r="B224" s="15"/>
       <c r="C224" s="42"/>
       <c r="D224" s="41"/>
       <c r="E224" s="41"/>
@@ -4953,7 +4634,7 @@
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="4"/>
-      <c r="B225" s="5"/>
+      <c r="B225" s="15"/>
       <c r="C225" s="42"/>
       <c r="D225" s="41"/>
       <c r="E225" s="41"/>
@@ -4963,7 +4644,7 @@
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="4"/>
-      <c r="B226" s="5"/>
+      <c r="B226" s="15"/>
       <c r="C226" s="42"/>
       <c r="D226" s="41"/>
       <c r="E226" s="41"/>
@@ -4973,7 +4654,7 @@
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" s="4"/>
-      <c r="B227" s="5"/>
+      <c r="B227" s="15"/>
       <c r="C227" s="42"/>
       <c r="D227" s="41"/>
       <c r="E227" s="41"/>
@@ -4983,7 +4664,7 @@
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="4"/>
-      <c r="B228" s="5"/>
+      <c r="B228" s="15"/>
       <c r="C228" s="42"/>
       <c r="D228" s="41"/>
       <c r="E228" s="41"/>
@@ -4993,7 +4674,7 @@
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="4"/>
-      <c r="B229" s="5"/>
+      <c r="B229" s="15"/>
       <c r="C229" s="42"/>
       <c r="D229" s="41"/>
       <c r="E229" s="41"/>
@@ -5003,7 +4684,7 @@
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="4"/>
-      <c r="B230" s="5"/>
+      <c r="B230" s="15"/>
       <c r="C230" s="42"/>
       <c r="D230" s="41"/>
       <c r="E230" s="41"/>
@@ -5013,7 +4694,7 @@
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="4"/>
-      <c r="B231" s="5"/>
+      <c r="B231" s="15"/>
       <c r="C231" s="42"/>
       <c r="D231" s="41"/>
       <c r="E231" s="41"/>
@@ -5023,7 +4704,7 @@
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="4"/>
-      <c r="B232" s="5"/>
+      <c r="B232" s="15"/>
       <c r="C232" s="42"/>
       <c r="D232" s="41"/>
       <c r="E232" s="41"/>
@@ -5033,7 +4714,7 @@
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="4"/>
-      <c r="B233" s="5"/>
+      <c r="B233" s="15"/>
       <c r="C233" s="42"/>
       <c r="D233" s="41"/>
       <c r="E233" s="41"/>
@@ -5043,7 +4724,7 @@
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="4"/>
-      <c r="B234" s="5"/>
+      <c r="B234" s="15"/>
       <c r="C234" s="42"/>
       <c r="D234" s="41"/>
       <c r="E234" s="41"/>
@@ -5053,7 +4734,7 @@
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="4"/>
-      <c r="B235" s="5"/>
+      <c r="B235" s="15"/>
       <c r="C235" s="42"/>
       <c r="D235" s="41"/>
       <c r="E235" s="41"/>
@@ -5063,7 +4744,7 @@
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="4"/>
-      <c r="B236" s="5"/>
+      <c r="B236" s="15"/>
       <c r="C236" s="42"/>
       <c r="D236" s="41"/>
       <c r="E236" s="41"/>
@@ -5073,7 +4754,7 @@
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" s="4"/>
-      <c r="B237" s="5"/>
+      <c r="B237" s="15"/>
       <c r="C237" s="42"/>
       <c r="D237" s="41"/>
       <c r="E237" s="41"/>
@@ -5083,7 +4764,7 @@
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" s="4"/>
-      <c r="B238" s="5"/>
+      <c r="B238" s="15"/>
       <c r="C238" s="42"/>
       <c r="D238" s="41"/>
       <c r="E238" s="41"/>
@@ -5093,7 +4774,7 @@
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="4"/>
-      <c r="B239" s="5"/>
+      <c r="B239" s="15"/>
       <c r="C239" s="42"/>
       <c r="D239" s="41"/>
       <c r="E239" s="41"/>
@@ -5103,7 +4784,7 @@
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" s="4"/>
-      <c r="B240" s="5"/>
+      <c r="B240" s="15"/>
       <c r="C240" s="42"/>
       <c r="D240" s="41"/>
       <c r="E240" s="41"/>
@@ -5113,7 +4794,7 @@
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="4"/>
-      <c r="B241" s="5"/>
+      <c r="B241" s="15"/>
       <c r="C241" s="42"/>
       <c r="D241" s="41"/>
       <c r="E241" s="41"/>
@@ -5123,7 +4804,7 @@
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" s="4"/>
-      <c r="B242" s="5"/>
+      <c r="B242" s="15"/>
       <c r="C242" s="42"/>
       <c r="D242" s="41"/>
       <c r="E242" s="41"/>
@@ -5133,7 +4814,7 @@
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="4"/>
-      <c r="B243" s="5"/>
+      <c r="B243" s="15"/>
       <c r="C243" s="42"/>
       <c r="D243" s="41"/>
       <c r="E243" s="41"/>
@@ -5143,7 +4824,7 @@
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="4"/>
-      <c r="B244" s="5"/>
+      <c r="B244" s="15"/>
       <c r="C244" s="42"/>
       <c r="D244" s="41"/>
       <c r="E244" s="41"/>
@@ -5153,7 +4834,7 @@
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="4"/>
-      <c r="B245" s="5"/>
+      <c r="B245" s="15"/>
       <c r="C245" s="42"/>
       <c r="D245" s="41"/>
       <c r="E245" s="41"/>
@@ -5163,7 +4844,7 @@
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" s="4"/>
-      <c r="B246" s="5"/>
+      <c r="B246" s="15"/>
       <c r="C246" s="42"/>
       <c r="D246" s="41"/>
       <c r="E246" s="41"/>
@@ -5173,7 +4854,7 @@
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" s="4"/>
-      <c r="B247" s="5"/>
+      <c r="B247" s="15"/>
       <c r="C247" s="42"/>
       <c r="D247" s="41"/>
       <c r="E247" s="41"/>
@@ -5183,7 +4864,7 @@
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" s="4"/>
-      <c r="B248" s="5"/>
+      <c r="B248" s="15"/>
       <c r="C248" s="42"/>
       <c r="D248" s="41"/>
       <c r="E248" s="41"/>
@@ -5193,7 +4874,7 @@
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" s="4"/>
-      <c r="B249" s="5"/>
+      <c r="B249" s="15"/>
       <c r="C249" s="42"/>
       <c r="D249" s="41"/>
       <c r="E249" s="41"/>
@@ -5203,7 +4884,7 @@
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" s="4"/>
-      <c r="B250" s="5"/>
+      <c r="B250" s="15"/>
       <c r="C250" s="42"/>
       <c r="D250" s="41"/>
       <c r="E250" s="41"/>
@@ -5213,7 +4894,7 @@
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" s="4"/>
-      <c r="B251" s="5"/>
+      <c r="B251" s="15"/>
       <c r="C251" s="42"/>
       <c r="D251" s="41"/>
       <c r="E251" s="41"/>
@@ -5223,7 +4904,7 @@
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="4"/>
-      <c r="B252" s="5"/>
+      <c r="B252" s="15"/>
       <c r="C252" s="42"/>
       <c r="D252" s="41"/>
       <c r="E252" s="41"/>
@@ -5233,7 +4914,7 @@
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" s="4"/>
-      <c r="B253" s="5"/>
+      <c r="B253" s="15"/>
       <c r="C253" s="42"/>
       <c r="D253" s="41"/>
       <c r="E253" s="41"/>
@@ -5243,7 +4924,7 @@
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" s="4"/>
-      <c r="B254" s="5"/>
+      <c r="B254" s="15"/>
       <c r="C254" s="42"/>
       <c r="D254" s="41"/>
       <c r="E254" s="41"/>
@@ -5253,7 +4934,7 @@
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" s="4"/>
-      <c r="B255" s="5"/>
+      <c r="B255" s="15"/>
       <c r="C255" s="42"/>
       <c r="D255" s="41"/>
       <c r="E255" s="41"/>
@@ -5263,7 +4944,7 @@
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" s="4"/>
-      <c r="B256" s="5"/>
+      <c r="B256" s="15"/>
       <c r="C256" s="42"/>
       <c r="D256" s="41"/>
       <c r="E256" s="41"/>
@@ -5273,7 +4954,7 @@
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257" s="4"/>
-      <c r="B257" s="5"/>
+      <c r="B257" s="15"/>
       <c r="C257" s="42"/>
       <c r="D257" s="41"/>
       <c r="E257" s="41"/>
@@ -5283,7 +4964,7 @@
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" s="4"/>
-      <c r="B258" s="5"/>
+      <c r="B258" s="15"/>
       <c r="C258" s="42"/>
       <c r="D258" s="41"/>
       <c r="E258" s="41"/>
@@ -5293,7 +4974,7 @@
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259" s="4"/>
-      <c r="B259" s="5"/>
+      <c r="B259" s="15"/>
       <c r="C259" s="42"/>
       <c r="D259" s="41"/>
       <c r="E259" s="41"/>
@@ -5303,7 +4984,7 @@
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" s="4"/>
-      <c r="B260" s="5"/>
+      <c r="B260" s="15"/>
       <c r="C260" s="42"/>
       <c r="D260" s="41"/>
       <c r="E260" s="41"/>
@@ -5313,7 +4994,7 @@
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" s="4"/>
-      <c r="B261" s="5"/>
+      <c r="B261" s="15"/>
       <c r="C261" s="42"/>
       <c r="D261" s="41"/>
       <c r="E261" s="41"/>
@@ -5323,7 +5004,7 @@
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" s="4"/>
-      <c r="B262" s="5"/>
+      <c r="B262" s="15"/>
       <c r="C262" s="42"/>
       <c r="D262" s="41"/>
       <c r="E262" s="41"/>
@@ -5333,7 +5014,7 @@
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263" s="4"/>
-      <c r="B263" s="5"/>
+      <c r="B263" s="15"/>
       <c r="C263" s="42"/>
       <c r="D263" s="41"/>
       <c r="E263" s="41"/>
@@ -5343,7 +5024,7 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" s="4"/>
-      <c r="B264" s="5"/>
+      <c r="B264" s="15"/>
       <c r="C264" s="42"/>
       <c r="D264" s="41"/>
       <c r="E264" s="41"/>
@@ -6873,34 +6554,44 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:B416">
-    <cfRule type="expression" dxfId="5" priority="4">
+  <conditionalFormatting sqref="D57 A50:B416">
+    <cfRule type="expression" dxfId="7" priority="7">
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C8:H27 C28:E28 G28:H28">
+  <conditionalFormatting sqref="D49:H56 C124:H416 D58:H123 E57:H57 C9:H48">
+    <cfRule type="expression" dxfId="6" priority="4">
+      <formula>MOD(ROW()-1,2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7:B7 A9:B9 A8:H8">
+    <cfRule type="expression" dxfId="5" priority="2">
+      <formula>MOD(ROW()-1,2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10 A10:A29 B12:B29 A30:B49">
     <cfRule type="expression" dxfId="4" priority="3">
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C29:H416">
+  <conditionalFormatting sqref="C7:H7">
     <cfRule type="expression" dxfId="3" priority="1">
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8:H416" xr:uid="{A3DF8C03-8B15-444D-AE35-1A6E2A7E55AE}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H9:H416 H7" xr:uid="{A3DF8C03-8B15-444D-AE35-1A6E2A7E55AE}">
       <formula1>1945</formula1>
       <formula2>2045</formula2>
     </dataValidation>
@@ -6920,7 +6611,7 @@
           <x14:formula1>
             <xm:f>LOV!$A$1:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>G8:G416</xm:sqref>
+          <xm:sqref>G124:G416</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6942,32 +6633,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="46"/>
+      <c r="B1" s="45"/>
       <c r="C1" s="52" t="s">
-        <v>151</v>
+        <v>51</v>
       </c>
       <c r="D1" s="53"/>
       <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="46"/>
+      <c r="B2" s="45"/>
       <c r="C2" s="52" t="s">
-        <v>183</v>
+        <v>55</v>
       </c>
       <c r="D2" s="53"/>
       <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="46"/>
+      <c r="B3" s="45"/>
       <c r="C3" s="52" t="s">
         <v>12</v>
       </c>
@@ -6975,10 +6666,10 @@
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="46"/>
+      <c r="B4" s="45"/>
       <c r="C4" s="52" t="s">
         <v>13</v>
       </c>
@@ -6987,19 +6678,19 @@
     </row>
     <row r="5" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="48" t="s">
+      <c r="A6" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="50" t="str">
+      <c r="B6" s="51"/>
+      <c r="C6" s="48" t="str">
         <f>"Collaborator Table - "&amp;C1&amp;" ("&amp;C2&amp;")"</f>
         <v>Collaborator Table - Argonne National Laboratory (Min, Misun)</v>
       </c>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="51"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="49"/>
     </row>
     <row r="7" spans="1:8" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
@@ -11226,15 +10917,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001733C14AC8EC6F498F123411DB8BC020" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c1f196d61ef494b6c4f62f58be5bb14e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7b7cc8fe-90e2-43f3-ad3c-00f457ec8258" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="46c76a5a58717c3453de3c52cd271f55" ns2:_="">
     <xsd:import namespace="7b7cc8fe-90e2-43f3-ad3c-00f457ec8258"/>
@@ -11366,6 +11048,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -11373,14 +11064,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53ACD002-FFBE-4185-9DDB-0AA3A824C3C1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE70D9AC-1270-4AD5-BB63-23D2B0A32B51}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11394,6 +11077,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53ACD002-FFBE-4185-9DDB-0AA3A824C3C1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/proposal/collaboration/collaboration_min.xlsx
+++ b/proposal/collaboration/collaboration_min.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/misunmin/proj/genesis21b/proposal/collaboration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F34D52B0-3720-924C-968B-ACC33436C0AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE044D2-610F-7146-982A-758B3358BCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4200" yWindow="660" windowWidth="30240" windowHeight="17640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2200" yWindow="660" windowWidth="30240" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="3" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="152">
   <si>
     <r>
       <rPr>
@@ -534,6 +534,9 @@
   </si>
   <si>
     <t>0000-0002-5646-5689</t>
+  </si>
+  <si>
+    <t>mmin@anl.gov</t>
   </si>
 </sst>
 </file>
@@ -1159,6 +1162,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1174,17 +1178,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1192,7 +1196,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1203,23 +1206,6 @@
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1254,6 +1240,23 @@
       <fill>
         <patternFill>
           <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1585,51 +1588,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="47" t="s">
+      <c r="B1" s="46"/>
+      <c r="C1" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="47"/>
+      <c r="D1" s="48"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="47" t="s">
+      <c r="B2" s="46"/>
+      <c r="C2" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="47"/>
+      <c r="D2" s="48"/>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="47" t="s">
+      <c r="B3" s="46"/>
+      <c r="C3" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="47"/>
+      <c r="D3" s="48"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="46" t="s">
+      <c r="B4" s="46"/>
+      <c r="C4" s="47" t="s">
         <v>149</v>
       </c>
-      <c r="D4" s="47"/>
+      <c r="D4" s="48"/>
     </row>
     <row r="5" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="44"/>
+      <c r="B6" s="45"/>
       <c r="C6" s="39"/>
       <c r="D6" s="40"/>
     </row>
@@ -1805,7 +1808,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H416"/>
+  <dimension ref="A1:I415"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="22.6640625" customWidth="1"/>
@@ -1816,66 +1819,66 @@
     <col min="8" max="8" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="47" t="s">
+      <c r="B1" s="46"/>
+      <c r="C1" s="48" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="47"/>
+      <c r="D1" s="48"/>
       <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="45" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="47" t="s">
+      <c r="B2" s="46"/>
+      <c r="C2" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="47"/>
+      <c r="D2" s="48"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="45" t="s">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="47" t="s">
+      <c r="B3" s="46"/>
+      <c r="C3" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="47"/>
+      <c r="D3" s="48"/>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="45" t="s">
+    <row r="4" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="46" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" s="47"/>
+      <c r="B4" s="46"/>
+      <c r="C4" s="47" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4" s="48"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="50" t="s">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="48" t="e">
+      <c r="B5" s="50"/>
+      <c r="C5" s="51" t="e">
         <f>"Collaborator Table - "&amp;#REF!&amp;" ("&amp;C1&amp;")"</f>
         <v>#REF!</v>
       </c>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="48"/>
-      <c r="H5" s="49"/>
-    </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="52"/>
+    </row>
+    <row r="6" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
         <v>6</v>
       </c>
@@ -1901,7 +1904,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="36.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="36.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
         <v>56</v>
       </c>
@@ -1925,33 +1928,32 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="15" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="G8" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="C8" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="19">
+        <v>2023</v>
+      </c>
+      <c r="I8" s="14"/>
+    </row>
+    <row r="9" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="s">
         <v>56</v>
       </c>
@@ -1959,14 +1961,14 @@
         <v>57</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E9" s="17"/>
       <c r="F9" s="17" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G9" s="18" t="s">
         <v>20</v>
@@ -1975,22 +1977,22 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="43" t="s">
         <v>57</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E10" s="17"/>
       <c r="F10" s="17" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="G10" s="18" t="s">
         <v>20</v>
@@ -1999,18 +2001,18 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="54" t="s">
+      <c r="B11" s="15" t="s">
         <v>57</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E11" s="17"/>
       <c r="F11" s="17" t="s">
@@ -2023,7 +2025,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="14" t="s">
         <v>56</v>
       </c>
@@ -2031,10 +2033,10 @@
         <v>57</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E12" s="17"/>
       <c r="F12" s="17" t="s">
@@ -2047,31 +2049,31 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C13" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="18" t="s">
+      <c r="C13" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="7">
         <v>2023</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
         <v>56</v>
       </c>
@@ -2079,9 +2081,9 @@
         <v>57</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>70</v>
-      </c>
-      <c r="D14" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="42" t="s">
         <v>32</v>
       </c>
       <c r="E14" s="41"/>
@@ -2095,7 +2097,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="s">
         <v>56</v>
       </c>
@@ -2103,10 +2105,10 @@
         <v>57</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" s="42" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="E15" s="41"/>
       <c r="F15" s="41" t="s">
@@ -2119,7 +2121,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="14" t="s">
         <v>56</v>
       </c>
@@ -2127,14 +2129,14 @@
         <v>57</v>
       </c>
       <c r="C16" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="D16" s="42" t="s">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="D16" s="41" t="s">
+        <v>75</v>
       </c>
       <c r="E16" s="41"/>
       <c r="F16" s="41" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>20</v>
@@ -2151,14 +2153,14 @@
         <v>57</v>
       </c>
       <c r="C17" s="42" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D17" s="41" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E17" s="41"/>
       <c r="F17" s="41" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>20</v>
@@ -2175,14 +2177,14 @@
         <v>57</v>
       </c>
       <c r="C18" s="42" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D18" s="41" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E18" s="41"/>
       <c r="F18" s="41" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>20</v>
@@ -2199,14 +2201,14 @@
         <v>57</v>
       </c>
       <c r="C19" s="42" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D19" s="41" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E19" s="41"/>
       <c r="F19" s="41" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="G19" s="6" t="s">
         <v>20</v>
@@ -2223,10 +2225,10 @@
         <v>57</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D20" s="41" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E20" s="41"/>
       <c r="F20" s="41" t="s">
@@ -2247,10 +2249,10 @@
         <v>57</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D21" s="41" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E21" s="41"/>
       <c r="F21" s="41" t="s">
@@ -2271,10 +2273,10 @@
         <v>57</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D22" s="41" t="s">
-        <v>88</v>
+        <v>48</v>
       </c>
       <c r="E22" s="41"/>
       <c r="F22" s="41" t="s">
@@ -2295,10 +2297,10 @@
         <v>57</v>
       </c>
       <c r="C23" s="42" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D23" s="41" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="E23" s="41"/>
       <c r="F23" s="41" t="s">
@@ -2319,10 +2321,10 @@
         <v>57</v>
       </c>
       <c r="C24" s="42" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D24" s="41" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="E24" s="41"/>
       <c r="F24" s="41" t="s">
@@ -2343,10 +2345,10 @@
         <v>57</v>
       </c>
       <c r="C25" s="42" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D25" s="41" t="s">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="E25" s="41"/>
       <c r="F25" s="41" t="s">
@@ -2367,10 +2369,10 @@
         <v>57</v>
       </c>
       <c r="C26" s="42" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D26" s="41" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E26" s="41"/>
       <c r="F26" s="41" t="s">
@@ -2391,10 +2393,10 @@
         <v>57</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D27" s="41" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E27" s="41"/>
       <c r="F27" s="41" t="s">
@@ -2415,10 +2417,10 @@
         <v>57</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="D28" s="41" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E28" s="41"/>
       <c r="F28" s="41" t="s">
@@ -2439,17 +2441,17 @@
         <v>57</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="D29" s="41" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E29" s="41"/>
       <c r="F29" s="41" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="H29" s="7">
         <v>2023</v>
@@ -2463,20 +2465,20 @@
         <v>57</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D30" s="41" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E30" s="41"/>
       <c r="F30" s="41" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H30" s="7">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2487,20 +2489,20 @@
         <v>57</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D31" s="41" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E31" s="41"/>
       <c r="F31" s="41" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H31" s="7">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2511,20 +2513,20 @@
         <v>57</v>
       </c>
       <c r="C32" s="42" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D32" s="41" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E32" s="41"/>
       <c r="F32" s="41" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>37</v>
       </c>
       <c r="H32" s="7">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2535,10 +2537,10 @@
         <v>57</v>
       </c>
       <c r="C33" s="42" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D33" s="41" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E33" s="41"/>
       <c r="F33" s="41" t="s">
@@ -2559,20 +2561,20 @@
         <v>57</v>
       </c>
       <c r="C34" s="42" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D34" s="41" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E34" s="41"/>
       <c r="F34" s="41" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>37</v>
       </c>
       <c r="H34" s="7">
-        <v>2022</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2583,20 +2585,20 @@
         <v>57</v>
       </c>
       <c r="C35" s="42" t="s">
-        <v>114</v>
+        <v>38</v>
       </c>
       <c r="D35" s="41" t="s">
-        <v>115</v>
+        <v>54</v>
       </c>
       <c r="E35" s="41"/>
       <c r="F35" s="41" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H35" s="7">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2607,20 +2609,20 @@
         <v>57</v>
       </c>
       <c r="C36" s="42" t="s">
-        <v>38</v>
+        <v>118</v>
       </c>
       <c r="D36" s="41" t="s">
-        <v>54</v>
+        <v>119</v>
       </c>
       <c r="E36" s="41"/>
       <c r="F36" s="41" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="H36" s="7">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2631,20 +2633,20 @@
         <v>57</v>
       </c>
       <c r="C37" s="42" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D37" s="41" t="s">
-        <v>119</v>
+        <v>47</v>
       </c>
       <c r="E37" s="41"/>
       <c r="F37" s="41" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H37" s="7">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2655,14 +2657,14 @@
         <v>57</v>
       </c>
       <c r="C38" s="42" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D38" s="41" t="s">
-        <v>47</v>
+        <v>124</v>
       </c>
       <c r="E38" s="41"/>
       <c r="F38" s="41" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>20</v>
@@ -2679,14 +2681,14 @@
         <v>57</v>
       </c>
       <c r="C39" s="42" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D39" s="41" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E39" s="41"/>
       <c r="F39" s="41" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>20</v>
@@ -2703,14 +2705,14 @@
         <v>57</v>
       </c>
       <c r="C40" s="42" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D40" s="41" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E40" s="41"/>
       <c r="F40" s="41" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>20</v>
@@ -2727,14 +2729,14 @@
         <v>57</v>
       </c>
       <c r="C41" s="42" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D41" s="41" t="s">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="E41" s="41"/>
       <c r="F41" s="41" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G41" s="6" t="s">
         <v>20</v>
@@ -2751,20 +2753,20 @@
         <v>57</v>
       </c>
       <c r="C42" s="42" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D42" s="41" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E42" s="41"/>
       <c r="F42" s="41" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>20</v>
       </c>
       <c r="H42" s="7">
-        <v>2023</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2775,20 +2777,20 @@
         <v>57</v>
       </c>
       <c r="C43" s="42" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D43" s="41" t="s">
-        <v>47</v>
+        <v>137</v>
       </c>
       <c r="E43" s="41"/>
       <c r="F43" s="41" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>20</v>
       </c>
       <c r="H43" s="7">
-        <v>2016</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2799,20 +2801,20 @@
         <v>57</v>
       </c>
       <c r="C44" s="42" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D44" s="41" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E44" s="41"/>
       <c r="F44" s="41" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>20</v>
       </c>
       <c r="H44" s="7">
-        <v>2018</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -2823,10 +2825,10 @@
         <v>57</v>
       </c>
       <c r="C45" s="42" t="s">
-        <v>139</v>
+        <v>53</v>
       </c>
       <c r="D45" s="41" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E45" s="41"/>
       <c r="F45" s="41" t="s">
@@ -2847,14 +2849,14 @@
         <v>57</v>
       </c>
       <c r="C46" s="42" t="s">
-        <v>53</v>
+        <v>143</v>
       </c>
       <c r="D46" s="41" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E46" s="41"/>
       <c r="F46" s="41" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>20</v>
@@ -2871,14 +2873,14 @@
         <v>57</v>
       </c>
       <c r="C47" s="42" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D47" s="41" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E47" s="41"/>
       <c r="F47" s="41" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G47" s="6" t="s">
         <v>20</v>
@@ -2887,43 +2889,26 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C48" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="D48" s="41" t="s">
-        <v>147</v>
-      </c>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" s="14"/>
+      <c r="B48" s="5"/>
+      <c r="D48" s="42"/>
       <c r="E48" s="41"/>
-      <c r="F48" s="41" t="s">
-        <v>148</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="F48" s="41"/>
+      <c r="G48" s="41"/>
       <c r="H48" s="7">
         <v>2023</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>57</v>
-      </c>
+      <c r="A49" s="14"/>
+      <c r="B49" s="15"/>
       <c r="D49" s="42"/>
       <c r="E49" s="41"/>
       <c r="F49" s="41"/>
       <c r="G49" s="41"/>
       <c r="H49" s="7">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -2934,7 +2919,7 @@
       <c r="F50" s="41"/>
       <c r="G50" s="41"/>
       <c r="H50" s="7">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
@@ -2967,7 +2952,7 @@
       <c r="F53" s="41"/>
       <c r="G53" s="41"/>
       <c r="H53" s="7">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
@@ -2978,7 +2963,7 @@
       <c r="F54" s="41"/>
       <c r="G54" s="41"/>
       <c r="H54" s="7">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
@@ -2989,29 +2974,29 @@
       <c r="F55" s="41"/>
       <c r="G55" s="41"/>
       <c r="H55" s="7">
-        <v>2019</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="14"/>
       <c r="B56" s="15"/>
-      <c r="D56" s="42"/>
+      <c r="D56" s="14"/>
       <c r="E56" s="41"/>
       <c r="F56" s="41"/>
       <c r="G56" s="41"/>
       <c r="H56" s="7">
-        <v>2023</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="14"/>
       <c r="B57" s="15"/>
-      <c r="D57" s="14"/>
+      <c r="D57" s="42"/>
       <c r="E57" s="41"/>
       <c r="F57" s="41"/>
       <c r="G57" s="41"/>
       <c r="H57" s="7">
-        <v>2019</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -3022,7 +3007,7 @@
       <c r="F58" s="41"/>
       <c r="G58" s="41"/>
       <c r="H58" s="7">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
@@ -3087,9 +3072,7 @@
       <c r="E64" s="41"/>
       <c r="F64" s="41"/>
       <c r="G64" s="41"/>
-      <c r="H64" s="7">
-        <v>2026</v>
-      </c>
+      <c r="H64" s="7"/>
     </row>
     <row r="65" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="14"/>
@@ -3101,7 +3084,7 @@
       <c r="H65" s="7"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A66" s="14"/>
+      <c r="A66" s="4"/>
       <c r="B66" s="15"/>
       <c r="D66" s="42"/>
       <c r="E66" s="41"/>
@@ -3616,10 +3599,11 @@
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="4"/>
       <c r="B123" s="15"/>
-      <c r="D123" s="42"/>
+      <c r="C123" s="42"/>
+      <c r="D123" s="41"/>
       <c r="E123" s="41"/>
       <c r="F123" s="41"/>
-      <c r="G123" s="41"/>
+      <c r="G123" s="6"/>
       <c r="H123" s="7"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
@@ -5024,7 +5008,7 @@
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" s="4"/>
-      <c r="B264" s="15"/>
+      <c r="B264" s="5"/>
       <c r="C264" s="42"/>
       <c r="D264" s="41"/>
       <c r="E264" s="41"/>
@@ -6532,25 +6516,15 @@
       <c r="G414" s="6"/>
       <c r="H414" s="7"/>
     </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A415" s="4"/>
-      <c r="B415" s="5"/>
-      <c r="C415" s="42"/>
-      <c r="D415" s="41"/>
-      <c r="E415" s="41"/>
-      <c r="F415" s="41"/>
-      <c r="G415" s="6"/>
-      <c r="H415" s="7"/>
-    </row>
-    <row r="416" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A416" s="8"/>
-      <c r="B416" s="9"/>
-      <c r="C416" s="10"/>
-      <c r="D416" s="11"/>
-      <c r="E416" s="11"/>
-      <c r="F416" s="11"/>
-      <c r="G416" s="12"/>
-      <c r="H416" s="13"/>
+    <row r="415" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A415" s="8"/>
+      <c r="B415" s="9"/>
+      <c r="C415" s="10"/>
+      <c r="D415" s="11"/>
+      <c r="E415" s="11"/>
+      <c r="F415" s="11"/>
+      <c r="G415" s="12"/>
+      <c r="H415" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -6565,33 +6539,33 @@
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
-  <conditionalFormatting sqref="D57 A50:B416">
-    <cfRule type="expression" dxfId="7" priority="7">
+  <conditionalFormatting sqref="A7:B8 I8">
+    <cfRule type="expression" dxfId="7" priority="2">
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D49:H56 C124:H416 D58:H123 E57:H57 C9:H48">
-    <cfRule type="expression" dxfId="6" priority="4">
-      <formula>MOD(ROW()-1,2)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7:B7 A9:B9 A8:H8">
-    <cfRule type="expression" dxfId="5" priority="2">
-      <formula>MOD(ROW()-1,2)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10 A10:A29 B12:B29 A30:B49">
-    <cfRule type="expression" dxfId="4" priority="3">
+  <conditionalFormatting sqref="B9 A9:A28 B11:B28 A29:B415">
+    <cfRule type="expression" dxfId="6" priority="3">
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C7:H7">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>MOD(ROW()-1,2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8:H47 D48:H55 E56:H56 D57:H122 C123:H415">
+    <cfRule type="expression" dxfId="4" priority="4">
+      <formula>MOD(ROW()-1,2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D56">
+    <cfRule type="expression" dxfId="3" priority="7">
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H9:H416 H7" xr:uid="{A3DF8C03-8B15-444D-AE35-1A6E2A7E55AE}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8:H415 H7" xr:uid="{A3DF8C03-8B15-444D-AE35-1A6E2A7E55AE}">
       <formula1>1945</formula1>
       <formula2>2045</formula2>
     </dataValidation>
@@ -6611,7 +6585,7 @@
           <x14:formula1>
             <xm:f>LOV!$A$1:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>G124:G416</xm:sqref>
+          <xm:sqref>G123:G415</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6633,64 +6607,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="52" t="s">
+      <c r="B1" s="46"/>
+      <c r="C1" s="53" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="53"/>
+      <c r="D1" s="54"/>
       <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="45"/>
-      <c r="C2" s="52" t="s">
+      <c r="B2" s="46"/>
+      <c r="C2" s="53" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="53"/>
+      <c r="D2" s="54"/>
       <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="45" t="s">
+      <c r="A3" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="52" t="s">
+      <c r="B3" s="46"/>
+      <c r="C3" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="53"/>
+      <c r="D3" s="54"/>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="52" t="s">
+      <c r="B4" s="46"/>
+      <c r="C4" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="53"/>
+      <c r="D4" s="54"/>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="50" t="s">
+      <c r="A6" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="51"/>
-      <c r="C6" s="48" t="str">
+      <c r="B6" s="50"/>
+      <c r="C6" s="51" t="str">
         <f>"Collaborator Table - "&amp;C1&amp;" ("&amp;C2&amp;")"</f>
         <v>Collaborator Table - Argonne National Laboratory (Min, Misun)</v>
       </c>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="49"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="52"/>
     </row>
     <row r="7" spans="1:8" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
@@ -10917,6 +10891,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001733C14AC8EC6F498F123411DB8BC020" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c1f196d61ef494b6c4f62f58be5bb14e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7b7cc8fe-90e2-43f3-ad3c-00f457ec8258" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="46c76a5a58717c3453de3c52cd271f55" ns2:_="">
     <xsd:import namespace="7b7cc8fe-90e2-43f3-ad3c-00f457ec8258"/>
@@ -11048,15 +11031,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -11064,6 +11038,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53ACD002-FFBE-4185-9DDB-0AA3A824C3C1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE70D9AC-1270-4AD5-BB63-23D2B0A32B51}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11077,14 +11059,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53ACD002-FFBE-4185-9DDB-0AA3A824C3C1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/proposal/collaboration/collaboration_min.xlsx
+++ b/proposal/collaboration/collaboration_min.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/misunmin/proj/genesis21b/proposal/collaboration/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/misunmin/proj/gm21b/proposal/collaboration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FE044D2-610F-7146-982A-758B3358BCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6157DE04-59FE-F24C-B956-D87D51D73B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2200" yWindow="660" windowWidth="30240" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2820" yWindow="1840" windowWidth="30240" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="3" r:id="rId1"/>
@@ -20,10 +20,10 @@
     <sheet name="LOV" sheetId="6" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">Collaborators!$C$6:$F$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">Collaborators!$C$6:$F$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Collaborators Example'!$C$6:$F$7</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Senior-Key Personnel'!$C$6:$D$7</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">Collaborators!$6:$7</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">Collaborators!$6:$6</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Collaborators Example'!$6:$7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Senior-Key Personnel'!$6:$7</definedName>
   </definedNames>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="147">
   <si>
     <r>
       <rPr>
@@ -239,9 +239,6 @@
     <t>Argonne National Laboratory</t>
   </si>
   <si>
-    <t>University of Illinois Urbana-Champaign</t>
-  </si>
-  <si>
     <t>Voronin</t>
   </si>
   <si>
@@ -257,12 +254,6 @@
     <t>Misun</t>
   </si>
   <si>
-    <t>Fischer</t>
-  </si>
-  <si>
-    <t>Paul</t>
-  </si>
-  <si>
     <t>Kerkemeier</t>
   </si>
   <si>
@@ -273,12 +264,6 @@
   </si>
   <si>
     <t>Aristotle University of Thessaloniki</t>
-  </si>
-  <si>
-    <t>Kolev</t>
-  </si>
-  <si>
-    <t>Tzanio</t>
   </si>
   <si>
     <t>Dobrev</t>
@@ -543,7 +528,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -564,13 +549,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1058,9 +1036,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1162,7 +1140,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1172,7 +1149,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1227,19 +1204,19 @@
       </fill>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color auto="1"/>
       </font>
       <fill>
         <patternFill>
           <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1588,51 +1565,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="48" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="48"/>
+      <c r="D1" s="47"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="48"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="47"/>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="48"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="47"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="47" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" s="48"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="47"/>
     </row>
     <row r="5" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="45"/>
+      <c r="B6" s="44"/>
       <c r="C6" s="39"/>
       <c r="D6" s="40"/>
     </row>
@@ -1652,13 +1629,13 @@
     </row>
     <row r="8" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="30" t="s">
-        <v>57</v>
-      </c>
       <c r="C8" s="31" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D8" s="32" t="s">
         <v>51</v>
@@ -1808,7 +1785,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I415"/>
+  <dimension ref="A1:I413"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="22.6640625" customWidth="1"/>
@@ -1820,63 +1797,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="48" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="47" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="48"/>
+      <c r="D1" s="47"/>
       <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="48"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="47"/>
       <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="48"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="47"/>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="47" t="s">
-        <v>151</v>
-      </c>
-      <c r="D4" s="48"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="46" t="s">
+        <v>146</v>
+      </c>
+      <c r="D4" s="47"/>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="51" t="e">
+      <c r="B5" s="49"/>
+      <c r="C5" s="50" t="e">
         <f>"Collaborator Table - "&amp;#REF!&amp;" ("&amp;C1&amp;")"</f>
         <v>#REF!</v>
       </c>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="52"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="51"/>
     </row>
     <row r="6" spans="1:9" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
@@ -1904,22 +1881,22 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="36.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="C7" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="16" t="s">
-        <v>58</v>
-      </c>
       <c r="D7" s="17" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="E7" s="17"/>
       <c r="F7" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G7" s="18" t="s">
         <v>20</v>
@@ -1927,23 +1904,24 @@
       <c r="H7" s="19">
         <v>2023</v>
       </c>
+      <c r="I7" s="14"/>
     </row>
     <row r="8" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>57</v>
-      </c>
       <c r="C8" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E8" s="17"/>
       <c r="F8" s="17" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G8" s="18" t="s">
         <v>20</v>
@@ -1951,14 +1929,13 @@
       <c r="H8" s="19">
         <v>2023</v>
       </c>
-      <c r="I8" s="14"/>
     </row>
     <row r="9" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="15" t="s">
         <v>56</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>57</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>61</v>
@@ -1968,7 +1945,7 @@
       </c>
       <c r="E9" s="17"/>
       <c r="F9" s="17" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="G9" s="18" t="s">
         <v>20</v>
@@ -1979,16 +1956,16 @@
     </row>
     <row r="10" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="43" t="s">
-        <v>57</v>
-      </c>
       <c r="C10" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="17" t="s">
         <v>64</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>65</v>
       </c>
       <c r="E10" s="17"/>
       <c r="F10" s="17" t="s">
@@ -2003,68 +1980,68 @@
     </row>
     <row r="11" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B11" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="D11" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11" s="18" t="s">
+      <c r="G11" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="7">
         <v>2023</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" s="18" t="s">
+      <c r="C12" s="42" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="7">
         <v>2023</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C13" s="42" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" s="41" t="s">
-        <v>32</v>
+        <v>68</v>
+      </c>
+      <c r="D13" s="42" t="s">
+        <v>68</v>
       </c>
       <c r="E13" s="41"/>
       <c r="F13" s="41" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G13" s="6" t="s">
         <v>20</v>
@@ -2075,16 +2052,16 @@
     </row>
     <row r="14" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C14" s="42" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="42" t="s">
-        <v>32</v>
+        <v>69</v>
+      </c>
+      <c r="D14" s="41" t="s">
+        <v>70</v>
       </c>
       <c r="E14" s="41"/>
       <c r="F14" s="41" t="s">
@@ -2099,20 +2076,20 @@
     </row>
     <row r="15" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C15" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="D15" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="41" t="s">
         <v>73</v>
       </c>
       <c r="E15" s="41"/>
       <c r="F15" s="41" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G15" s="6" t="s">
         <v>20</v>
@@ -2123,20 +2100,20 @@
     </row>
     <row r="16" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C16" s="42" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D16" s="41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E16" s="41"/>
       <c r="F16" s="41" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G16" s="6" t="s">
         <v>20</v>
@@ -2147,20 +2124,20 @@
     </row>
     <row r="17" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C17" s="42" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D17" s="41" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E17" s="41"/>
       <c r="F17" s="41" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="G17" s="6" t="s">
         <v>20</v>
@@ -2171,10 +2148,10 @@
     </row>
     <row r="18" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>57</v>
       </c>
       <c r="C18" s="42" t="s">
         <v>80</v>
@@ -2184,7 +2161,7 @@
       </c>
       <c r="E18" s="41"/>
       <c r="F18" s="41" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>20</v>
@@ -2195,16 +2172,16 @@
     </row>
     <row r="19" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C19" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" s="41" t="s">
         <v>83</v>
-      </c>
-      <c r="D19" s="41" t="s">
-        <v>84</v>
       </c>
       <c r="E19" s="41"/>
       <c r="F19" s="41" t="s">
@@ -2219,16 +2196,16 @@
     </row>
     <row r="20" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C20" s="42" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D20" s="41" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="E20" s="41"/>
       <c r="F20" s="41" t="s">
@@ -2243,16 +2220,16 @@
     </row>
     <row r="21" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C21" s="42" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D21" s="41" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E21" s="41"/>
       <c r="F21" s="41" t="s">
@@ -2267,16 +2244,16 @@
     </row>
     <row r="22" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C22" s="42" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D22" s="41" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E22" s="41"/>
       <c r="F22" s="41" t="s">
@@ -2291,16 +2268,16 @@
     </row>
     <row r="23" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C23" s="42" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D23" s="41" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E23" s="41"/>
       <c r="F23" s="41" t="s">
@@ -2315,16 +2292,16 @@
     </row>
     <row r="24" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C24" s="42" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D24" s="41" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="E24" s="41"/>
       <c r="F24" s="41" t="s">
@@ -2339,16 +2316,16 @@
     </row>
     <row r="25" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C25" s="42" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" s="41" t="s">
         <v>93</v>
-      </c>
-      <c r="D25" s="41" t="s">
-        <v>94</v>
       </c>
       <c r="E25" s="41"/>
       <c r="F25" s="41" t="s">
@@ -2363,16 +2340,16 @@
     </row>
     <row r="26" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C26" s="42" t="s">
-        <v>95</v>
+        <v>49</v>
       </c>
       <c r="D26" s="41" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E26" s="41"/>
       <c r="F26" s="41" t="s">
@@ -2387,23 +2364,23 @@
     </row>
     <row r="27" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C27" s="42" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D27" s="41" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E27" s="41"/>
       <c r="F27" s="41" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="H27" s="7">
         <v>2023</v>
@@ -2411,44 +2388,44 @@
     </row>
     <row r="28" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C28" s="42" t="s">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="D28" s="41" t="s">
         <v>99</v>
       </c>
       <c r="E28" s="41"/>
       <c r="F28" s="41" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="H28" s="7">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C29" s="42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D29" s="41" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E29" s="41"/>
       <c r="F29" s="41" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G29" s="6" t="s">
         <v>37</v>
@@ -2459,58 +2436,58 @@
     </row>
     <row r="30" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C30" s="42" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D30" s="41" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E30" s="41"/>
       <c r="F30" s="41" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="H30" s="7">
-        <v>2020</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C31" s="42" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D31" s="41" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E31" s="41"/>
       <c r="F31" s="41" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G31" s="6" t="s">
         <v>37</v>
       </c>
       <c r="H31" s="7">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>57</v>
       </c>
       <c r="C32" s="42" t="s">
         <v>109</v>
@@ -2526,49 +2503,49 @@
         <v>37</v>
       </c>
       <c r="H32" s="7">
-        <v>2022</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C33" s="42" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="D33" s="41" t="s">
-        <v>113</v>
+        <v>53</v>
       </c>
       <c r="E33" s="41"/>
       <c r="F33" s="41" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G33" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H33" s="7">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C34" s="42" t="s">
+        <v>113</v>
+      </c>
+      <c r="D34" s="41" t="s">
         <v>114</v>
-      </c>
-      <c r="D34" s="41" t="s">
-        <v>115</v>
       </c>
       <c r="E34" s="41"/>
       <c r="F34" s="41" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>37</v>
@@ -2579,16 +2556,16 @@
     </row>
     <row r="35" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C35" s="42" t="s">
-        <v>38</v>
+        <v>116</v>
       </c>
       <c r="D35" s="41" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E35" s="41"/>
       <c r="F35" s="41" t="s">
@@ -2603,10 +2580,10 @@
     </row>
     <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>57</v>
       </c>
       <c r="C36" s="42" t="s">
         <v>118</v>
@@ -2619,28 +2596,28 @@
         <v>120</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="H36" s="7">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>57</v>
       </c>
       <c r="C37" s="42" t="s">
         <v>121</v>
       </c>
       <c r="D37" s="41" t="s">
-        <v>47</v>
+        <v>122</v>
       </c>
       <c r="E37" s="41"/>
       <c r="F37" s="41" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>20</v>
@@ -2651,20 +2628,20 @@
     </row>
     <row r="38" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C38" s="42" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D38" s="41" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E38" s="41"/>
       <c r="F38" s="41" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>20</v>
@@ -2675,16 +2652,16 @@
     </row>
     <row r="39" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C39" s="42" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D39" s="41" t="s">
-        <v>127</v>
+        <v>44</v>
       </c>
       <c r="E39" s="41"/>
       <c r="F39" s="41" t="s">
@@ -2699,40 +2676,40 @@
     </row>
     <row r="40" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B40" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>57</v>
       </c>
       <c r="C40" s="42" t="s">
         <v>129</v>
       </c>
       <c r="D40" s="41" t="s">
-        <v>130</v>
+        <v>47</v>
       </c>
       <c r="E40" s="41"/>
       <c r="F40" s="41" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>20</v>
       </c>
       <c r="H40" s="7">
-        <v>2023</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C41" s="42" t="s">
+        <v>131</v>
+      </c>
+      <c r="D41" s="41" t="s">
         <v>132</v>
-      </c>
-      <c r="D41" s="41" t="s">
-        <v>44</v>
       </c>
       <c r="E41" s="41"/>
       <c r="F41" s="41" t="s">
@@ -2742,73 +2719,73 @@
         <v>20</v>
       </c>
       <c r="H41" s="7">
-        <v>2023</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>57</v>
       </c>
       <c r="C42" s="42" t="s">
         <v>134</v>
       </c>
       <c r="D42" s="41" t="s">
-        <v>47</v>
+        <v>135</v>
       </c>
       <c r="E42" s="41"/>
       <c r="F42" s="41" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>20</v>
       </c>
       <c r="H42" s="7">
-        <v>2016</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C43" s="42" t="s">
-        <v>136</v>
+        <v>52</v>
       </c>
       <c r="D43" s="41" t="s">
         <v>137</v>
       </c>
       <c r="E43" s="41"/>
       <c r="F43" s="41" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="G43" s="6" t="s">
         <v>20</v>
       </c>
       <c r="H43" s="7">
-        <v>2018</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C44" s="42" t="s">
+        <v>138</v>
+      </c>
+      <c r="D44" s="41" t="s">
         <v>139</v>
-      </c>
-      <c r="D44" s="41" t="s">
-        <v>140</v>
       </c>
       <c r="E44" s="41"/>
       <c r="F44" s="41" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G44" s="6" t="s">
         <v>20</v>
@@ -2819,20 +2796,20 @@
     </row>
     <row r="45" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="C45" s="42" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
       <c r="D45" s="41" t="s">
         <v>142</v>
       </c>
       <c r="E45" s="41"/>
       <c r="F45" s="41" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>20</v>
@@ -2841,63 +2818,37 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A46" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C46" s="42" t="s">
-        <v>143</v>
-      </c>
-      <c r="D46" s="41" t="s">
-        <v>144</v>
-      </c>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A46" s="14"/>
+      <c r="B46" s="5"/>
+      <c r="D46" s="42"/>
       <c r="E46" s="41"/>
-      <c r="F46" s="41" t="s">
-        <v>145</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="F46" s="41"/>
+      <c r="G46" s="41"/>
       <c r="H46" s="7">
         <v>2023</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A47" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C47" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="D47" s="41" t="s">
-        <v>147</v>
-      </c>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" s="14"/>
+      <c r="B47" s="15"/>
+      <c r="D47" s="42"/>
       <c r="E47" s="41"/>
-      <c r="F47" s="41" t="s">
-        <v>148</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="F47" s="41"/>
+      <c r="G47" s="41"/>
       <c r="H47" s="7">
-        <v>2023</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="14"/>
-      <c r="B48" s="5"/>
+      <c r="B48" s="15"/>
       <c r="D48" s="42"/>
       <c r="E48" s="41"/>
       <c r="F48" s="41"/>
       <c r="G48" s="41"/>
       <c r="H48" s="7">
-        <v>2023</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
@@ -2908,7 +2859,7 @@
       <c r="F49" s="41"/>
       <c r="G49" s="41"/>
       <c r="H49" s="7">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
@@ -2930,7 +2881,7 @@
       <c r="F51" s="41"/>
       <c r="G51" s="41"/>
       <c r="H51" s="7">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
@@ -2952,13 +2903,13 @@
       <c r="F53" s="41"/>
       <c r="G53" s="41"/>
       <c r="H53" s="7">
-        <v>2020</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="14"/>
       <c r="B54" s="15"/>
-      <c r="D54" s="42"/>
+      <c r="D54" s="14"/>
       <c r="E54" s="41"/>
       <c r="F54" s="41"/>
       <c r="G54" s="41"/>
@@ -2974,18 +2925,18 @@
       <c r="F55" s="41"/>
       <c r="G55" s="41"/>
       <c r="H55" s="7">
-        <v>2023</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="14"/>
       <c r="B56" s="15"/>
-      <c r="D56" s="14"/>
+      <c r="D56" s="42"/>
       <c r="E56" s="41"/>
       <c r="F56" s="41"/>
       <c r="G56" s="41"/>
       <c r="H56" s="7">
-        <v>2019</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
@@ -2996,7 +2947,7 @@
       <c r="F57" s="41"/>
       <c r="G57" s="41"/>
       <c r="H57" s="7">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
@@ -3050,23 +3001,19 @@
       <c r="E62" s="41"/>
       <c r="F62" s="41"/>
       <c r="G62" s="41"/>
-      <c r="H62" s="7">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H62" s="7"/>
+    </row>
+    <row r="63" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="14"/>
       <c r="B63" s="15"/>
       <c r="D63" s="42"/>
       <c r="E63" s="41"/>
       <c r="F63" s="41"/>
       <c r="G63" s="41"/>
-      <c r="H63" s="7">
-        <v>2026</v>
-      </c>
+      <c r="H63" s="7"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" s="14"/>
+      <c r="A64" s="4"/>
       <c r="B64" s="15"/>
       <c r="D64" s="42"/>
       <c r="E64" s="41"/>
@@ -3074,8 +3021,8 @@
       <c r="G64" s="41"/>
       <c r="H64" s="7"/>
     </row>
-    <row r="65" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="14"/>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A65" s="4"/>
       <c r="B65" s="15"/>
       <c r="D65" s="42"/>
       <c r="E65" s="41"/>
@@ -3581,19 +3528,21 @@
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="4"/>
       <c r="B121" s="15"/>
-      <c r="D121" s="42"/>
+      <c r="C121" s="42"/>
+      <c r="D121" s="41"/>
       <c r="E121" s="41"/>
       <c r="F121" s="41"/>
-      <c r="G121" s="41"/>
+      <c r="G121" s="6"/>
       <c r="H121" s="7"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="4"/>
       <c r="B122" s="15"/>
-      <c r="D122" s="42"/>
+      <c r="C122" s="42"/>
+      <c r="D122" s="41"/>
       <c r="E122" s="41"/>
       <c r="F122" s="41"/>
-      <c r="G122" s="41"/>
+      <c r="G122" s="6"/>
       <c r="H122" s="7"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
@@ -4988,7 +4937,7 @@
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" s="4"/>
-      <c r="B262" s="15"/>
+      <c r="B262" s="5"/>
       <c r="C262" s="42"/>
       <c r="D262" s="41"/>
       <c r="E262" s="41"/>
@@ -4998,7 +4947,7 @@
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263" s="4"/>
-      <c r="B263" s="15"/>
+      <c r="B263" s="5"/>
       <c r="C263" s="42"/>
       <c r="D263" s="41"/>
       <c r="E263" s="41"/>
@@ -6496,35 +6445,15 @@
       <c r="G412" s="6"/>
       <c r="H412" s="7"/>
     </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A413" s="4"/>
-      <c r="B413" s="5"/>
-      <c r="C413" s="42"/>
-      <c r="D413" s="41"/>
-      <c r="E413" s="41"/>
-      <c r="F413" s="41"/>
-      <c r="G413" s="6"/>
-      <c r="H413" s="7"/>
-    </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A414" s="4"/>
-      <c r="B414" s="5"/>
-      <c r="C414" s="42"/>
-      <c r="D414" s="41"/>
-      <c r="E414" s="41"/>
-      <c r="F414" s="41"/>
-      <c r="G414" s="6"/>
-      <c r="H414" s="7"/>
-    </row>
-    <row r="415" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A415" s="8"/>
-      <c r="B415" s="9"/>
-      <c r="C415" s="10"/>
-      <c r="D415" s="11"/>
-      <c r="E415" s="11"/>
-      <c r="F415" s="11"/>
-      <c r="G415" s="12"/>
-      <c r="H415" s="13"/>
+    <row r="413" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A413" s="8"/>
+      <c r="B413" s="9"/>
+      <c r="C413" s="10"/>
+      <c r="D413" s="11"/>
+      <c r="E413" s="11"/>
+      <c r="F413" s="11"/>
+      <c r="G413" s="12"/>
+      <c r="H413" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -6539,33 +6468,33 @@
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="C4:D4"/>
   </mergeCells>
-  <conditionalFormatting sqref="A7:B8 I8">
+  <conditionalFormatting sqref="I7 A7:B7 A8:A26">
     <cfRule type="expression" dxfId="7" priority="2">
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B9 A9:A28 B11:B28 A29:B415">
+  <conditionalFormatting sqref="B8:B26 A27:B413">
     <cfRule type="expression" dxfId="6" priority="3">
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C7:H7">
+  <conditionalFormatting sqref="C7:H45">
     <cfRule type="expression" dxfId="5" priority="1">
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C8:H47 D48:H55 E56:H56 D57:H122 C123:H415">
-    <cfRule type="expression" dxfId="4" priority="4">
+  <conditionalFormatting sqref="D54">
+    <cfRule type="expression" dxfId="4" priority="7">
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D56">
-    <cfRule type="expression" dxfId="3" priority="7">
+  <conditionalFormatting sqref="D46:H53 E54:H54 D55:H120 C121:H413">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>MOD(ROW()-1,2)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H8:H415 H7" xr:uid="{A3DF8C03-8B15-444D-AE35-1A6E2A7E55AE}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7:H413" xr:uid="{A3DF8C03-8B15-444D-AE35-1A6E2A7E55AE}">
       <formula1>1945</formula1>
       <formula2>2045</formula2>
     </dataValidation>
@@ -6585,7 +6514,7 @@
           <x14:formula1>
             <xm:f>LOV!$A$1:$A$6</xm:f>
           </x14:formula1>
-          <xm:sqref>G123:G415</xm:sqref>
+          <xm:sqref>G121:G413</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6607,64 +6536,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="53" t="s">
+      <c r="B1" s="45"/>
+      <c r="C1" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="54"/>
+      <c r="D1" s="53"/>
       <c r="E1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="53" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="54"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="53"/>
       <c r="E2" s="3"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="46" t="s">
+      <c r="A3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="46"/>
-      <c r="C3" s="53" t="s">
+      <c r="B3" s="45"/>
+      <c r="C3" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="54"/>
+      <c r="D3" s="53"/>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="46" t="s">
+      <c r="A4" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="46"/>
-      <c r="C4" s="53" t="s">
+      <c r="B4" s="45"/>
+      <c r="C4" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="54"/>
+      <c r="D4" s="53"/>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="51" t="str">
+      <c r="B6" s="49"/>
+      <c r="C6" s="50" t="str">
         <f>"Collaborator Table - "&amp;C1&amp;" ("&amp;C2&amp;")"</f>
         <v>Collaborator Table - Argonne National Laboratory (Min, Misun)</v>
       </c>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="52"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="51"/>
     </row>
     <row r="7" spans="1:8" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
@@ -10891,15 +10820,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001733C14AC8EC6F498F123411DB8BC020" ma:contentTypeVersion="2" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c1f196d61ef494b6c4f62f58be5bb14e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7b7cc8fe-90e2-43f3-ad3c-00f457ec8258" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="46c76a5a58717c3453de3c52cd271f55" ns2:_="">
     <xsd:import namespace="7b7cc8fe-90e2-43f3-ad3c-00f457ec8258"/>
@@ -11031,6 +10951,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -11038,14 +10967,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53ACD002-FFBE-4185-9DDB-0AA3A824C3C1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BE70D9AC-1270-4AD5-BB63-23D2B0A32B51}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11059,6 +10980,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53ACD002-FFBE-4185-9DDB-0AA3A824C3C1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
